--- a/samples/exam-underperforming-final/store_month_costs.xlsx
+++ b/samples/exam-underperforming-final/store_month_costs.xlsx
@@ -620,64 +620,64 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>3481.84</v>
+        <v>2646.02</v>
       </c>
       <c r="D2">
-        <v>417.82</v>
+        <v>317.52</v>
       </c>
       <c r="E2">
-        <v>227.5</v>
+        <v>417.44</v>
       </c>
       <c r="F2">
-        <v>123.85</v>
+        <v>191</v>
       </c>
       <c r="G2">
-        <v>105.44</v>
+        <v>122.08</v>
       </c>
       <c r="H2">
-        <v>58.35</v>
+        <v>86</v>
       </c>
       <c r="I2">
-        <v>204.3</v>
+        <v>244</v>
       </c>
       <c r="J2">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>9529</v>
+        <v>14471</v>
       </c>
       <c r="L2">
-        <v>2669.3</v>
+        <v>4567.37</v>
       </c>
       <c r="M2">
-        <v>3.83</v>
+        <v>93.7</v>
       </c>
       <c r="N2">
-        <v>232</v>
+        <v>90</v>
       </c>
       <c r="O2">
-        <v>4.1</v>
+        <v>44.68</v>
       </c>
       <c r="P2">
-        <v>75.25</v>
+        <v>65</v>
       </c>
       <c r="Q2">
-        <v>0.4</v>
+        <v>110.68</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>306.7</v>
       </c>
       <c r="S2">
-        <v>17247.28</v>
+        <v>23466.49</v>
       </c>
       <c r="T2">
-        <v>615.03</v>
+        <v>22339.56</v>
       </c>
       <c r="U2">
-        <v>512.53</v>
+        <v>18616.27</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -688,64 +688,64 @@
         <v>23</v>
       </c>
       <c r="C3">
-        <v>3481.84</v>
+        <v>2646.02</v>
       </c>
       <c r="D3">
-        <v>417.82</v>
+        <v>317.52</v>
       </c>
       <c r="E3">
-        <v>227.5</v>
+        <v>417.44</v>
       </c>
       <c r="F3">
-        <v>123.85</v>
+        <v>191</v>
       </c>
       <c r="G3">
-        <v>105.44</v>
+        <v>122.08</v>
       </c>
       <c r="H3">
-        <v>58.35</v>
+        <v>86</v>
       </c>
       <c r="I3">
-        <v>204.3</v>
+        <v>244</v>
       </c>
       <c r="J3">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>9529</v>
+        <v>14471</v>
       </c>
       <c r="L3">
-        <v>2669.3</v>
+        <v>4567.37</v>
       </c>
       <c r="M3">
-        <v>2.41</v>
+        <v>89.49</v>
       </c>
       <c r="N3">
-        <v>232</v>
+        <v>90</v>
       </c>
       <c r="O3">
-        <v>2.58</v>
+        <v>42.67</v>
       </c>
       <c r="P3">
-        <v>75.25</v>
+        <v>65</v>
       </c>
       <c r="Q3">
-        <v>0.2</v>
+        <v>107.72</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="S3">
-        <v>17244.14</v>
+        <v>23457.31</v>
       </c>
       <c r="T3">
-        <v>386.6</v>
+        <v>21336.82</v>
       </c>
       <c r="U3">
-        <v>322.16</v>
+        <v>17780.73</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -756,64 +756,64 @@
         <v>23</v>
       </c>
       <c r="C4">
-        <v>3481.84</v>
+        <v>2646.02</v>
       </c>
       <c r="D4">
-        <v>417.82</v>
+        <v>317.52</v>
       </c>
       <c r="E4">
-        <v>199.56</v>
+        <v>366.18</v>
       </c>
       <c r="F4">
-        <v>123.85</v>
+        <v>191</v>
       </c>
       <c r="G4">
-        <v>105.44</v>
+        <v>122.08</v>
       </c>
       <c r="H4">
-        <v>58.35</v>
+        <v>86</v>
       </c>
       <c r="I4">
-        <v>204.3</v>
+        <v>244</v>
       </c>
       <c r="J4">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>9529</v>
+        <v>14471</v>
       </c>
       <c r="L4">
-        <v>2669.3</v>
+        <v>4567.37</v>
       </c>
       <c r="M4">
-        <v>5.75</v>
+        <v>105.25</v>
       </c>
       <c r="N4">
-        <v>232</v>
+        <v>90</v>
       </c>
       <c r="O4">
-        <v>6.16</v>
+        <v>50.19</v>
       </c>
       <c r="P4">
-        <v>75.25</v>
+        <v>65</v>
       </c>
       <c r="Q4">
-        <v>0.61</v>
+        <v>132.04</v>
       </c>
       <c r="R4">
-        <v>19.1</v>
+        <v>193.3</v>
       </c>
       <c r="S4">
-        <v>17223.53</v>
+        <v>23453.65</v>
       </c>
       <c r="T4">
-        <v>923.7</v>
+        <v>25094.17</v>
       </c>
       <c r="U4">
-        <v>769.75</v>
+        <v>20911.95</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -824,64 +824,64 @@
         <v>23</v>
       </c>
       <c r="C5">
-        <v>3481.84</v>
+        <v>2646.02</v>
       </c>
       <c r="D5">
-        <v>417.82</v>
+        <v>317.52</v>
       </c>
       <c r="E5">
-        <v>199.56</v>
+        <v>366.18</v>
       </c>
       <c r="F5">
-        <v>123.85</v>
+        <v>191</v>
       </c>
       <c r="G5">
-        <v>105.44</v>
+        <v>122.08</v>
       </c>
       <c r="H5">
-        <v>58.35</v>
+        <v>86</v>
       </c>
       <c r="I5">
-        <v>204.3</v>
+        <v>244</v>
       </c>
       <c r="J5">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>9529</v>
+        <v>14471</v>
       </c>
       <c r="L5">
-        <v>2669.3</v>
+        <v>4567.37</v>
       </c>
       <c r="M5">
-        <v>9.71</v>
+        <v>124.69</v>
       </c>
       <c r="N5">
-        <v>232</v>
+        <v>99.09</v>
       </c>
       <c r="O5">
-        <v>10.4</v>
+        <v>59.46</v>
       </c>
       <c r="P5">
-        <v>75.25</v>
+        <v>65</v>
       </c>
       <c r="Q5">
-        <v>0.44</v>
+        <v>160.07</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>315.4</v>
       </c>
       <c r="S5">
-        <v>17231.56</v>
+        <v>23519.48</v>
       </c>
       <c r="T5">
-        <v>1559.85</v>
+        <v>29728.03</v>
       </c>
       <c r="U5">
-        <v>1299.86</v>
+        <v>24773.3</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -892,64 +892,64 @@
         <v>23</v>
       </c>
       <c r="C6">
-        <v>3481.84</v>
+        <v>2646.02</v>
       </c>
       <c r="D6">
-        <v>417.82</v>
+        <v>317.52</v>
       </c>
       <c r="E6">
-        <v>199.56</v>
+        <v>366.18</v>
       </c>
       <c r="F6">
-        <v>123.85</v>
+        <v>191</v>
       </c>
       <c r="G6">
-        <v>105.44</v>
+        <v>122.08</v>
       </c>
       <c r="H6">
-        <v>58.35</v>
+        <v>86</v>
       </c>
       <c r="I6">
-        <v>204.3</v>
+        <v>244</v>
       </c>
       <c r="J6">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>9529</v>
+        <v>14471</v>
       </c>
       <c r="L6">
-        <v>2669.3</v>
+        <v>4567.37</v>
       </c>
       <c r="M6">
-        <v>8.07</v>
+        <v>116.54</v>
       </c>
       <c r="N6">
-        <v>232</v>
+        <v>92.62</v>
       </c>
       <c r="O6">
-        <v>8.64</v>
+        <v>55.57</v>
       </c>
       <c r="P6">
-        <v>75.25</v>
+        <v>65</v>
       </c>
       <c r="Q6">
-        <v>0.73</v>
+        <v>153.13</v>
       </c>
       <c r="R6">
-        <v>36.6</v>
+        <v>365.4</v>
       </c>
       <c r="S6">
-        <v>17228.45</v>
+        <v>23494.03</v>
       </c>
       <c r="T6">
-        <v>1296.56</v>
+        <v>27786.64</v>
       </c>
       <c r="U6">
-        <v>1080.46</v>
+        <v>23155.55</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -960,64 +960,64 @@
         <v>23</v>
       </c>
       <c r="C7">
-        <v>3481.84</v>
+        <v>2646.02</v>
       </c>
       <c r="D7">
-        <v>417.82</v>
+        <v>317.52</v>
       </c>
       <c r="E7">
-        <v>215.53</v>
+        <v>395.47</v>
       </c>
       <c r="F7">
-        <v>123.85</v>
+        <v>191</v>
       </c>
       <c r="G7">
-        <v>105.44</v>
+        <v>122.08</v>
       </c>
       <c r="H7">
-        <v>58.35</v>
+        <v>86</v>
       </c>
       <c r="I7">
-        <v>204.3</v>
+        <v>244</v>
       </c>
       <c r="J7">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>9529</v>
+        <v>14471</v>
       </c>
       <c r="L7">
-        <v>2669.3</v>
+        <v>4567.37</v>
       </c>
       <c r="M7">
-        <v>1.22</v>
+        <v>94.23</v>
       </c>
       <c r="N7">
-        <v>232</v>
+        <v>90</v>
       </c>
       <c r="O7">
-        <v>1.31</v>
+        <v>44.93</v>
       </c>
       <c r="P7">
-        <v>75.25</v>
+        <v>65</v>
       </c>
       <c r="Q7">
-        <v>0.05</v>
+        <v>126.48</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>217.6</v>
       </c>
       <c r="S7">
-        <v>17229.56</v>
+        <v>23461.1</v>
       </c>
       <c r="T7">
-        <v>196.43</v>
+        <v>22466.2</v>
       </c>
       <c r="U7">
-        <v>163.69</v>
+        <v>18721.81</v>
       </c>
       <c r="V7">
-        <v>2</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -1028,64 +1028,64 @@
         <v>23</v>
       </c>
       <c r="C8">
-        <v>3481.84</v>
+        <v>2646.02</v>
       </c>
       <c r="D8">
-        <v>417.82</v>
+        <v>317.52</v>
       </c>
       <c r="E8">
-        <v>215.53</v>
+        <v>395.47</v>
       </c>
       <c r="F8">
-        <v>123.85</v>
+        <v>191</v>
       </c>
       <c r="G8">
-        <v>105.44</v>
+        <v>122.08</v>
       </c>
       <c r="H8">
-        <v>58.35</v>
+        <v>86</v>
       </c>
       <c r="I8">
-        <v>204.3</v>
+        <v>244</v>
       </c>
       <c r="J8">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>9529</v>
+        <v>14471</v>
       </c>
       <c r="L8">
-        <v>2669.3</v>
+        <v>4567.37</v>
       </c>
       <c r="M8">
-        <v>6.39</v>
+        <v>113.06</v>
       </c>
       <c r="N8">
-        <v>232</v>
+        <v>90</v>
       </c>
       <c r="O8">
-        <v>6.84</v>
+        <v>53.91</v>
       </c>
       <c r="P8">
-        <v>75.25</v>
+        <v>65</v>
       </c>
       <c r="Q8">
-        <v>0.68</v>
+        <v>152.58</v>
       </c>
       <c r="R8">
-        <v>15.7</v>
+        <v>82</v>
       </c>
       <c r="S8">
-        <v>17240.89</v>
+        <v>23515.01</v>
       </c>
       <c r="T8">
-        <v>1026.74</v>
+        <v>26956.6</v>
       </c>
       <c r="U8">
-        <v>855.61</v>
+        <v>22463.78</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -1096,64 +1096,64 @@
         <v>23</v>
       </c>
       <c r="C9">
-        <v>3481.84</v>
+        <v>2646.02</v>
       </c>
       <c r="D9">
-        <v>417.82</v>
+        <v>317.52</v>
       </c>
       <c r="E9">
-        <v>215.53</v>
+        <v>395.47</v>
       </c>
       <c r="F9">
-        <v>123.85</v>
+        <v>191</v>
       </c>
       <c r="G9">
-        <v>105.44</v>
+        <v>122.08</v>
       </c>
       <c r="H9">
-        <v>58.35</v>
+        <v>86</v>
       </c>
       <c r="I9">
-        <v>204.3</v>
+        <v>244</v>
       </c>
       <c r="J9">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>9529</v>
+        <v>14471</v>
       </c>
       <c r="L9">
-        <v>2669.3</v>
+        <v>4567.37</v>
       </c>
       <c r="M9">
-        <v>8.83</v>
+        <v>115.3</v>
       </c>
       <c r="N9">
-        <v>232</v>
+        <v>91.63</v>
       </c>
       <c r="O9">
-        <v>9.45</v>
+        <v>54.98</v>
       </c>
       <c r="P9">
-        <v>75.25</v>
+        <v>65</v>
       </c>
       <c r="Q9">
-        <v>0.54</v>
+        <v>154.3</v>
       </c>
       <c r="R9">
-        <v>30.9</v>
+        <v>290.5</v>
       </c>
       <c r="S9">
-        <v>17245.8</v>
+        <v>23521.67</v>
       </c>
       <c r="T9">
-        <v>1417.45</v>
+        <v>27489.48</v>
       </c>
       <c r="U9">
-        <v>1181.21</v>
+        <v>22907.87</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -1164,64 +1164,64 @@
         <v>23</v>
       </c>
       <c r="C10">
-        <v>3481.84</v>
+        <v>2646.02</v>
       </c>
       <c r="D10">
-        <v>417.82</v>
+        <v>317.52</v>
       </c>
       <c r="E10">
-        <v>199.56</v>
+        <v>366.18</v>
       </c>
       <c r="F10">
-        <v>123.85</v>
+        <v>191</v>
       </c>
       <c r="G10">
-        <v>105.44</v>
+        <v>122.08</v>
       </c>
       <c r="H10">
-        <v>58.35</v>
+        <v>86</v>
       </c>
       <c r="I10">
-        <v>204.3</v>
+        <v>244</v>
       </c>
       <c r="J10">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>9529</v>
+        <v>14471</v>
       </c>
       <c r="L10">
-        <v>2669.3</v>
+        <v>4567.37</v>
       </c>
       <c r="M10">
-        <v>2.5</v>
+        <v>120.1</v>
       </c>
       <c r="N10">
-        <v>232</v>
+        <v>95.45</v>
       </c>
       <c r="O10">
-        <v>2.67</v>
+        <v>57.27</v>
       </c>
       <c r="P10">
-        <v>75.25</v>
+        <v>65</v>
       </c>
       <c r="Q10">
-        <v>0.26</v>
+        <v>161.72</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>309.4</v>
       </c>
       <c r="S10">
-        <v>17216.44</v>
+        <v>23510.71</v>
       </c>
       <c r="T10">
-        <v>401.23</v>
+        <v>28633.84</v>
       </c>
       <c r="U10">
-        <v>334.36</v>
+        <v>23861.64</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -1232,64 +1232,64 @@
         <v>23</v>
       </c>
       <c r="C11">
-        <v>3481.84</v>
+        <v>2646.02</v>
       </c>
       <c r="D11">
-        <v>417.82</v>
+        <v>317.52</v>
       </c>
       <c r="E11">
-        <v>199.56</v>
+        <v>366.18</v>
       </c>
       <c r="F11">
-        <v>123.85</v>
+        <v>191</v>
       </c>
       <c r="G11">
-        <v>105.44</v>
+        <v>122.08</v>
       </c>
       <c r="H11">
-        <v>58.35</v>
+        <v>86</v>
       </c>
       <c r="I11">
-        <v>204.3</v>
+        <v>244</v>
       </c>
       <c r="J11">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>9529</v>
+        <v>14471</v>
       </c>
       <c r="L11">
-        <v>2669.3</v>
+        <v>4567.37</v>
       </c>
       <c r="M11">
-        <v>8.93</v>
+        <v>140.19</v>
       </c>
       <c r="N11">
-        <v>232</v>
+        <v>111.41</v>
       </c>
       <c r="O11">
-        <v>9.56</v>
+        <v>66.85</v>
       </c>
       <c r="P11">
-        <v>75.25</v>
+        <v>65</v>
       </c>
       <c r="Q11">
-        <v>0.86</v>
+        <v>182.26</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>189.3</v>
       </c>
       <c r="S11">
-        <v>17230.36</v>
+        <v>23576.88</v>
       </c>
       <c r="T11">
-        <v>1434.13</v>
+        <v>33424.24</v>
       </c>
       <c r="U11">
-        <v>1195.1</v>
+        <v>27853.56</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -1300,64 +1300,64 @@
         <v>23</v>
       </c>
       <c r="C12">
-        <v>3481.84</v>
+        <v>2646.02</v>
       </c>
       <c r="D12">
-        <v>417.82</v>
+        <v>317.52</v>
       </c>
       <c r="E12">
-        <v>199.56</v>
+        <v>366.18</v>
       </c>
       <c r="F12">
-        <v>123.85</v>
+        <v>191</v>
       </c>
       <c r="G12">
-        <v>105.44</v>
+        <v>122.08</v>
       </c>
       <c r="H12">
-        <v>58.35</v>
+        <v>86</v>
       </c>
       <c r="I12">
-        <v>204.3</v>
+        <v>244</v>
       </c>
       <c r="J12">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>9529</v>
+        <v>14471</v>
       </c>
       <c r="L12">
-        <v>2669.3</v>
+        <v>4567.37</v>
       </c>
       <c r="M12">
-        <v>11.13</v>
+        <v>127.09</v>
       </c>
       <c r="N12">
-        <v>232</v>
+        <v>101</v>
       </c>
       <c r="O12">
-        <v>11.91</v>
+        <v>60.6</v>
       </c>
       <c r="P12">
-        <v>75.25</v>
+        <v>65</v>
       </c>
       <c r="Q12">
-        <v>1.02</v>
+        <v>164.67</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>293.4</v>
       </c>
       <c r="S12">
-        <v>17235.07</v>
+        <v>23529.53</v>
       </c>
       <c r="T12">
-        <v>1787.09</v>
+        <v>30301.17</v>
       </c>
       <c r="U12">
-        <v>1489.25</v>
+        <v>25250.89</v>
       </c>
       <c r="V12">
-        <v>13</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -1368,64 +1368,64 @@
         <v>23</v>
       </c>
       <c r="C13">
-        <v>3481.84</v>
+        <v>2646.02</v>
       </c>
       <c r="D13">
-        <v>417.82</v>
+        <v>317.52</v>
       </c>
       <c r="E13">
-        <v>227.5</v>
+        <v>417.44</v>
       </c>
       <c r="F13">
-        <v>123.85</v>
+        <v>191</v>
       </c>
       <c r="G13">
-        <v>105.44</v>
+        <v>122.08</v>
       </c>
       <c r="H13">
-        <v>58.35</v>
+        <v>86</v>
       </c>
       <c r="I13">
-        <v>204.3</v>
+        <v>244</v>
       </c>
       <c r="J13">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>9529</v>
+        <v>14471</v>
       </c>
       <c r="L13">
-        <v>2669.3</v>
+        <v>4567.37</v>
       </c>
       <c r="M13">
-        <v>4.67</v>
+        <v>160.91</v>
       </c>
       <c r="N13">
-        <v>232</v>
+        <v>127.89</v>
       </c>
       <c r="O13">
-        <v>4.99</v>
+        <v>76.73</v>
       </c>
       <c r="P13">
-        <v>75.25</v>
+        <v>65</v>
       </c>
       <c r="Q13">
-        <v>0.49</v>
+        <v>213.38</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="S13">
-        <v>17249.1</v>
+        <v>23706.34</v>
       </c>
       <c r="T13">
-        <v>749.2</v>
+        <v>38365.9</v>
       </c>
       <c r="U13">
-        <v>624.33</v>
+        <v>31971.55</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -1436,64 +1436,64 @@
         <v>35</v>
       </c>
       <c r="C14">
-        <v>3537.8</v>
+        <v>2981.95</v>
       </c>
       <c r="D14">
-        <v>424.54</v>
+        <v>357.83</v>
       </c>
       <c r="E14">
-        <v>915.87</v>
+        <v>179.18</v>
       </c>
       <c r="F14">
-        <v>300.65</v>
+        <v>108.55</v>
       </c>
       <c r="G14">
-        <v>164.07</v>
+        <v>97.56</v>
       </c>
       <c r="H14">
-        <v>131.15</v>
+        <v>52.05</v>
       </c>
       <c r="I14">
-        <v>330.7</v>
+        <v>198.9</v>
       </c>
       <c r="J14">
-        <v>176.7</v>
+        <v>108.9</v>
       </c>
       <c r="K14">
-        <v>20951</v>
+        <v>13645</v>
       </c>
       <c r="L14">
-        <v>6396.32</v>
+        <v>4662.98</v>
       </c>
       <c r="M14">
-        <v>3.5</v>
+        <v>165.35</v>
       </c>
       <c r="N14">
-        <v>137</v>
+        <v>263.93</v>
       </c>
       <c r="O14">
-        <v>3.55</v>
+        <v>156.16</v>
       </c>
       <c r="P14">
-        <v>97.25</v>
+        <v>70.75</v>
       </c>
       <c r="Q14">
-        <v>0.58</v>
+        <v>114.45</v>
       </c>
       <c r="R14">
-        <v>23</v>
+        <v>173.1</v>
       </c>
       <c r="S14">
-        <v>33570.68</v>
+        <v>23163.54</v>
       </c>
       <c r="T14">
-        <v>1182.3</v>
+        <v>26393.25</v>
       </c>
       <c r="U14">
-        <v>985.25</v>
+        <v>21994.52</v>
       </c>
       <c r="V14">
-        <v>12</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -1504,64 +1504,64 @@
         <v>35</v>
       </c>
       <c r="C15">
-        <v>3537.8</v>
+        <v>2981.95</v>
       </c>
       <c r="D15">
-        <v>424.54</v>
+        <v>357.83</v>
       </c>
       <c r="E15">
-        <v>915.87</v>
+        <v>179.18</v>
       </c>
       <c r="F15">
-        <v>300.65</v>
+        <v>108.55</v>
       </c>
       <c r="G15">
-        <v>164.07</v>
+        <v>97.56</v>
       </c>
       <c r="H15">
-        <v>131.15</v>
+        <v>52.05</v>
       </c>
       <c r="I15">
-        <v>330.7</v>
+        <v>198.9</v>
       </c>
       <c r="J15">
-        <v>176.7</v>
+        <v>108.9</v>
       </c>
       <c r="K15">
-        <v>20951</v>
+        <v>13645</v>
       </c>
       <c r="L15">
-        <v>6396.32</v>
+        <v>4662.98</v>
       </c>
       <c r="M15">
-        <v>4.63</v>
+        <v>154.78</v>
       </c>
       <c r="N15">
-        <v>137</v>
+        <v>247.06</v>
       </c>
       <c r="O15">
-        <v>4.69</v>
+        <v>146.18</v>
       </c>
       <c r="P15">
-        <v>97.25</v>
+        <v>70.75</v>
       </c>
       <c r="Q15">
-        <v>0.69</v>
+        <v>118.31</v>
       </c>
       <c r="R15">
-        <v>22.3</v>
+        <v>228.5</v>
       </c>
       <c r="S15">
-        <v>33573.06</v>
+        <v>23129.98</v>
       </c>
       <c r="T15">
-        <v>1563.21</v>
+        <v>24706.24</v>
       </c>
       <c r="U15">
-        <v>1302.68</v>
+        <v>20588.61</v>
       </c>
       <c r="V15">
-        <v>13</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -1572,64 +1572,64 @@
         <v>35</v>
       </c>
       <c r="C16">
-        <v>3537.8</v>
+        <v>2981.95</v>
       </c>
       <c r="D16">
-        <v>424.54</v>
+        <v>357.83</v>
       </c>
       <c r="E16">
-        <v>803.4</v>
+        <v>157.18</v>
       </c>
       <c r="F16">
-        <v>300.65</v>
+        <v>108.55</v>
       </c>
       <c r="G16">
-        <v>164.07</v>
+        <v>97.56</v>
       </c>
       <c r="H16">
-        <v>131.15</v>
+        <v>52.05</v>
       </c>
       <c r="I16">
-        <v>330.7</v>
+        <v>198.9</v>
       </c>
       <c r="J16">
-        <v>176.7</v>
+        <v>108.9</v>
       </c>
       <c r="K16">
-        <v>20951</v>
+        <v>13645</v>
       </c>
       <c r="L16">
-        <v>6396.32</v>
+        <v>4662.98</v>
       </c>
       <c r="M16">
-        <v>3.81</v>
+        <v>190.52</v>
       </c>
       <c r="N16">
-        <v>137</v>
+        <v>304.11</v>
       </c>
       <c r="O16">
-        <v>3.86</v>
+        <v>179.93</v>
       </c>
       <c r="P16">
-        <v>97.25</v>
+        <v>70.75</v>
       </c>
       <c r="Q16">
-        <v>0.71</v>
+        <v>150.31</v>
       </c>
       <c r="R16">
-        <v>33.4</v>
+        <v>210.3</v>
       </c>
       <c r="S16">
-        <v>33458.96</v>
+        <v>23266.52</v>
       </c>
       <c r="T16">
-        <v>1286.52</v>
+        <v>30410.4</v>
       </c>
       <c r="U16">
-        <v>1072.11</v>
+        <v>25342.1</v>
       </c>
       <c r="V16">
-        <v>13</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
@@ -1640,64 +1640,64 @@
         <v>35</v>
       </c>
       <c r="C17">
-        <v>3537.8</v>
+        <v>2981.95</v>
       </c>
       <c r="D17">
-        <v>424.54</v>
+        <v>357.83</v>
       </c>
       <c r="E17">
-        <v>803.4</v>
+        <v>157.18</v>
       </c>
       <c r="F17">
-        <v>300.65</v>
+        <v>108.55</v>
       </c>
       <c r="G17">
-        <v>164.07</v>
+        <v>97.56</v>
       </c>
       <c r="H17">
-        <v>131.15</v>
+        <v>52.05</v>
       </c>
       <c r="I17">
-        <v>330.7</v>
+        <v>198.9</v>
       </c>
       <c r="J17">
-        <v>176.7</v>
+        <v>108.9</v>
       </c>
       <c r="K17">
-        <v>20951</v>
+        <v>13645</v>
       </c>
       <c r="L17">
-        <v>6396.32</v>
+        <v>4662.98</v>
       </c>
       <c r="M17">
-        <v>7.56</v>
+        <v>204.05</v>
       </c>
       <c r="N17">
-        <v>137</v>
+        <v>325.7</v>
       </c>
       <c r="O17">
-        <v>7.67</v>
+        <v>192.7</v>
       </c>
       <c r="P17">
-        <v>97.25</v>
+        <v>70.75</v>
       </c>
       <c r="Q17">
-        <v>1.48</v>
+        <v>157.23</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>321.1</v>
       </c>
       <c r="S17">
-        <v>33467.29</v>
+        <v>23321.33</v>
       </c>
       <c r="T17">
-        <v>2555.48</v>
+        <v>32569.64</v>
       </c>
       <c r="U17">
-        <v>2129.58</v>
+        <v>27141.54</v>
       </c>
       <c r="V17">
-        <v>25</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
@@ -1708,64 +1708,64 @@
         <v>35</v>
       </c>
       <c r="C18">
-        <v>3537.8</v>
+        <v>2981.95</v>
       </c>
       <c r="D18">
-        <v>424.54</v>
+        <v>357.83</v>
       </c>
       <c r="E18">
-        <v>803.4</v>
+        <v>157.18</v>
       </c>
       <c r="F18">
-        <v>300.65</v>
+        <v>108.55</v>
       </c>
       <c r="G18">
-        <v>164.07</v>
+        <v>97.56</v>
       </c>
       <c r="H18">
-        <v>131.15</v>
+        <v>52.05</v>
       </c>
       <c r="I18">
-        <v>330.7</v>
+        <v>198.9</v>
       </c>
       <c r="J18">
-        <v>176.7</v>
+        <v>108.9</v>
       </c>
       <c r="K18">
-        <v>20951</v>
+        <v>13645</v>
       </c>
       <c r="L18">
-        <v>6396.32</v>
+        <v>4662.98</v>
       </c>
       <c r="M18">
-        <v>4.03</v>
+        <v>205.4</v>
       </c>
       <c r="N18">
-        <v>137</v>
+        <v>327.85</v>
       </c>
       <c r="O18">
-        <v>4.08</v>
+        <v>193.98</v>
       </c>
       <c r="P18">
-        <v>97.25</v>
+        <v>70.75</v>
       </c>
       <c r="Q18">
-        <v>0.65</v>
+        <v>163.36</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>288.3</v>
       </c>
       <c r="S18">
-        <v>33459.34</v>
+        <v>23332.24</v>
       </c>
       <c r="T18">
-        <v>1360</v>
+        <v>32785.23</v>
       </c>
       <c r="U18">
-        <v>1133.34</v>
+        <v>27321.09</v>
       </c>
       <c r="V18">
-        <v>12</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -1776,64 +1776,64 @@
         <v>35</v>
       </c>
       <c r="C19">
-        <v>3537.8</v>
+        <v>2981.95</v>
       </c>
       <c r="D19">
-        <v>424.54</v>
+        <v>357.83</v>
       </c>
       <c r="E19">
-        <v>867.67</v>
+        <v>169.75</v>
       </c>
       <c r="F19">
-        <v>300.65</v>
+        <v>108.55</v>
       </c>
       <c r="G19">
-        <v>164.07</v>
+        <v>97.56</v>
       </c>
       <c r="H19">
-        <v>131.15</v>
+        <v>52.05</v>
       </c>
       <c r="I19">
-        <v>330.7</v>
+        <v>198.9</v>
       </c>
       <c r="J19">
-        <v>176.7</v>
+        <v>108.9</v>
       </c>
       <c r="K19">
-        <v>20951</v>
+        <v>13645</v>
       </c>
       <c r="L19">
-        <v>6396.32</v>
+        <v>4662.98</v>
       </c>
       <c r="M19">
-        <v>4.03</v>
+        <v>171.15</v>
       </c>
       <c r="N19">
-        <v>137</v>
+        <v>273.19</v>
       </c>
       <c r="O19">
-        <v>4.08</v>
+        <v>161.64</v>
       </c>
       <c r="P19">
-        <v>97.25</v>
+        <v>70.75</v>
       </c>
       <c r="Q19">
-        <v>0.58</v>
+        <v>137.92</v>
       </c>
       <c r="R19">
-        <v>40.7</v>
+        <v>195.4</v>
       </c>
       <c r="S19">
-        <v>33523.54</v>
+        <v>23198.12</v>
       </c>
       <c r="T19">
-        <v>1361.2</v>
+        <v>27318.63</v>
       </c>
       <c r="U19">
-        <v>1134.33</v>
+        <v>22765.67</v>
       </c>
       <c r="V19">
-        <v>15</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -1844,64 +1844,64 @@
         <v>35</v>
       </c>
       <c r="C20">
-        <v>3537.8</v>
+        <v>2981.95</v>
       </c>
       <c r="D20">
-        <v>424.54</v>
+        <v>357.83</v>
       </c>
       <c r="E20">
-        <v>867.67</v>
+        <v>169.75</v>
       </c>
       <c r="F20">
-        <v>300.65</v>
+        <v>108.55</v>
       </c>
       <c r="G20">
-        <v>164.07</v>
+        <v>97.56</v>
       </c>
       <c r="H20">
-        <v>131.15</v>
+        <v>52.05</v>
       </c>
       <c r="I20">
-        <v>330.7</v>
+        <v>198.9</v>
       </c>
       <c r="J20">
-        <v>176.7</v>
+        <v>108.9</v>
       </c>
       <c r="K20">
-        <v>20951</v>
+        <v>13645</v>
       </c>
       <c r="L20">
-        <v>6396.32</v>
+        <v>4662.98</v>
       </c>
       <c r="M20">
-        <v>4.34</v>
+        <v>168.61</v>
       </c>
       <c r="N20">
-        <v>137</v>
+        <v>269.13</v>
       </c>
       <c r="O20">
-        <v>4.4</v>
+        <v>159.24</v>
       </c>
       <c r="P20">
-        <v>97.25</v>
+        <v>70.75</v>
       </c>
       <c r="Q20">
-        <v>0.5</v>
+        <v>139.4</v>
       </c>
       <c r="R20">
-        <v>28.2</v>
+        <v>193.8</v>
       </c>
       <c r="S20">
-        <v>33524.09</v>
+        <v>23190.6</v>
       </c>
       <c r="T20">
-        <v>1466.52</v>
+        <v>26912.97</v>
       </c>
       <c r="U20">
-        <v>1222.11</v>
+        <v>22427.61</v>
       </c>
       <c r="V20">
-        <v>17</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -1912,64 +1912,64 @@
         <v>35</v>
       </c>
       <c r="C21">
-        <v>3537.8</v>
+        <v>2981.95</v>
       </c>
       <c r="D21">
-        <v>424.54</v>
+        <v>357.83</v>
       </c>
       <c r="E21">
-        <v>867.67</v>
+        <v>169.75</v>
       </c>
       <c r="F21">
-        <v>300.65</v>
+        <v>108.55</v>
       </c>
       <c r="G21">
-        <v>164.07</v>
+        <v>97.56</v>
       </c>
       <c r="H21">
-        <v>131.15</v>
+        <v>52.05</v>
       </c>
       <c r="I21">
-        <v>330.7</v>
+        <v>198.9</v>
       </c>
       <c r="J21">
-        <v>176.7</v>
+        <v>108.9</v>
       </c>
       <c r="K21">
-        <v>20951</v>
+        <v>13645</v>
       </c>
       <c r="L21">
-        <v>6396.32</v>
+        <v>4662.98</v>
       </c>
       <c r="M21">
-        <v>9.14</v>
+        <v>190.64</v>
       </c>
       <c r="N21">
-        <v>137</v>
+        <v>304.29</v>
       </c>
       <c r="O21">
-        <v>9.26</v>
+        <v>180.04</v>
       </c>
       <c r="P21">
-        <v>97.25</v>
+        <v>70.75</v>
       </c>
       <c r="Q21">
-        <v>1.54</v>
+        <v>147.06</v>
       </c>
       <c r="R21">
-        <v>23.7</v>
+        <v>344.2</v>
       </c>
       <c r="S21">
-        <v>33534.79</v>
+        <v>23276.25</v>
       </c>
       <c r="T21">
-        <v>3087.68</v>
+        <v>30428.8</v>
       </c>
       <c r="U21">
-        <v>2573.06</v>
+        <v>25357.49</v>
       </c>
       <c r="V21">
-        <v>30</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
@@ -1980,64 +1980,64 @@
         <v>35</v>
       </c>
       <c r="C22">
-        <v>3537.8</v>
+        <v>2981.95</v>
       </c>
       <c r="D22">
-        <v>424.54</v>
+        <v>357.83</v>
       </c>
       <c r="E22">
-        <v>803.4</v>
+        <v>157.18</v>
       </c>
       <c r="F22">
-        <v>300.65</v>
+        <v>108.55</v>
       </c>
       <c r="G22">
-        <v>164.07</v>
+        <v>97.56</v>
       </c>
       <c r="H22">
-        <v>131.15</v>
+        <v>52.05</v>
       </c>
       <c r="I22">
-        <v>330.7</v>
+        <v>198.9</v>
       </c>
       <c r="J22">
-        <v>176.7</v>
+        <v>108.9</v>
       </c>
       <c r="K22">
-        <v>20951</v>
+        <v>13645</v>
       </c>
       <c r="L22">
-        <v>6396.32</v>
+        <v>4662.98</v>
       </c>
       <c r="M22">
-        <v>8.04</v>
+        <v>196.8</v>
       </c>
       <c r="N22">
-        <v>137</v>
+        <v>314.13</v>
       </c>
       <c r="O22">
-        <v>8.15</v>
+        <v>185.86</v>
       </c>
       <c r="P22">
-        <v>97.25</v>
+        <v>70.75</v>
       </c>
       <c r="Q22">
-        <v>1.25</v>
+        <v>150.68</v>
       </c>
       <c r="R22">
-        <v>28.4</v>
+        <v>287.9</v>
       </c>
       <c r="S22">
-        <v>33468.02</v>
+        <v>23289.12</v>
       </c>
       <c r="T22">
-        <v>2717.29</v>
+        <v>31412.57</v>
       </c>
       <c r="U22">
-        <v>2264.44</v>
+        <v>26177.25</v>
       </c>
       <c r="V22">
-        <v>24</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
@@ -2048,64 +2048,64 @@
         <v>35</v>
       </c>
       <c r="C23">
-        <v>3537.8</v>
+        <v>2981.95</v>
       </c>
       <c r="D23">
-        <v>424.54</v>
+        <v>357.83</v>
       </c>
       <c r="E23">
-        <v>803.4</v>
+        <v>157.18</v>
       </c>
       <c r="F23">
-        <v>300.65</v>
+        <v>108.55</v>
       </c>
       <c r="G23">
-        <v>164.07</v>
+        <v>97.56</v>
       </c>
       <c r="H23">
-        <v>131.15</v>
+        <v>52.05</v>
       </c>
       <c r="I23">
-        <v>330.7</v>
+        <v>198.9</v>
       </c>
       <c r="J23">
-        <v>176.7</v>
+        <v>108.9</v>
       </c>
       <c r="K23">
-        <v>20951</v>
+        <v>13645</v>
       </c>
       <c r="L23">
-        <v>6396.32</v>
+        <v>4662.98</v>
       </c>
       <c r="M23">
-        <v>9.05</v>
+        <v>258.33</v>
       </c>
       <c r="N23">
-        <v>137</v>
+        <v>412.33</v>
       </c>
       <c r="O23">
-        <v>9.18</v>
+        <v>243.96</v>
       </c>
       <c r="P23">
-        <v>97.25</v>
+        <v>70.75</v>
       </c>
       <c r="Q23">
-        <v>1.63</v>
+        <v>219.09</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>282.2</v>
       </c>
       <c r="S23">
-        <v>33470.44</v>
+        <v>23575.36</v>
       </c>
       <c r="T23">
-        <v>3058.48</v>
+        <v>41233.17</v>
       </c>
       <c r="U23">
-        <v>2548.72</v>
+        <v>34361.21</v>
       </c>
       <c r="V23">
-        <v>29</v>
+        <v>297</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
@@ -2116,64 +2116,64 @@
         <v>35</v>
       </c>
       <c r="C24">
-        <v>3537.8</v>
+        <v>2981.95</v>
       </c>
       <c r="D24">
-        <v>424.54</v>
+        <v>357.83</v>
       </c>
       <c r="E24">
-        <v>803.4</v>
+        <v>157.18</v>
       </c>
       <c r="F24">
-        <v>300.65</v>
+        <v>108.55</v>
       </c>
       <c r="G24">
-        <v>164.07</v>
+        <v>97.56</v>
       </c>
       <c r="H24">
-        <v>131.15</v>
+        <v>52.05</v>
       </c>
       <c r="I24">
-        <v>330.7</v>
+        <v>198.9</v>
       </c>
       <c r="J24">
-        <v>176.7</v>
+        <v>108.9</v>
       </c>
       <c r="K24">
-        <v>20951</v>
+        <v>13645</v>
       </c>
       <c r="L24">
-        <v>6396.32</v>
+        <v>4662.98</v>
       </c>
       <c r="M24">
-        <v>7.78</v>
+        <v>227.31</v>
       </c>
       <c r="N24">
-        <v>137</v>
+        <v>362.82</v>
       </c>
       <c r="O24">
-        <v>7.88</v>
+        <v>214.67</v>
       </c>
       <c r="P24">
-        <v>97.25</v>
+        <v>70.75</v>
       </c>
       <c r="Q24">
-        <v>1.09</v>
+        <v>194.08</v>
       </c>
       <c r="R24">
-        <v>13.5</v>
+        <v>388</v>
       </c>
       <c r="S24">
-        <v>33467.33</v>
+        <v>23440.53</v>
       </c>
       <c r="T24">
-        <v>2627.32</v>
+        <v>36282.05</v>
       </c>
       <c r="U24">
-        <v>2189.43</v>
+        <v>30235.17</v>
       </c>
       <c r="V24">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
@@ -2184,64 +2184,64 @@
         <v>35</v>
       </c>
       <c r="C25">
-        <v>3537.8</v>
+        <v>2981.95</v>
       </c>
       <c r="D25">
-        <v>424.54</v>
+        <v>357.83</v>
       </c>
       <c r="E25">
-        <v>915.87</v>
+        <v>179.18</v>
       </c>
       <c r="F25">
-        <v>300.65</v>
+        <v>108.55</v>
       </c>
       <c r="G25">
-        <v>164.07</v>
+        <v>97.56</v>
       </c>
       <c r="H25">
-        <v>131.15</v>
+        <v>52.05</v>
       </c>
       <c r="I25">
-        <v>330.7</v>
+        <v>198.9</v>
       </c>
       <c r="J25">
-        <v>176.7</v>
+        <v>108.9</v>
       </c>
       <c r="K25">
-        <v>20951</v>
+        <v>13645</v>
       </c>
       <c r="L25">
-        <v>6396.32</v>
+        <v>4662.98</v>
       </c>
       <c r="M25">
-        <v>12.74</v>
+        <v>298.67</v>
       </c>
       <c r="N25">
-        <v>137</v>
+        <v>476.73</v>
       </c>
       <c r="O25">
-        <v>12.91</v>
+        <v>282.07</v>
       </c>
       <c r="P25">
-        <v>97.25</v>
+        <v>70.75</v>
       </c>
       <c r="Q25">
-        <v>2.26</v>
+        <v>237.84</v>
       </c>
       <c r="R25">
-        <v>111.4</v>
+        <v>304.9</v>
       </c>
       <c r="S25">
-        <v>33590.96</v>
+        <v>23758.96</v>
       </c>
       <c r="T25">
-        <v>4304.54</v>
+        <v>47673.09</v>
       </c>
       <c r="U25">
-        <v>3587.15</v>
+        <v>39727.75</v>
       </c>
       <c r="V25">
-        <v>38</v>
+        <v>351</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
@@ -2252,64 +2252,64 @@
         <v>36</v>
       </c>
       <c r="C26">
-        <v>3455.36</v>
+        <v>3938.35</v>
       </c>
       <c r="D26">
-        <v>414.64</v>
+        <v>472.6</v>
       </c>
       <c r="E26">
-        <v>549.39</v>
+        <v>409.82</v>
       </c>
       <c r="F26">
-        <v>243.7</v>
+        <v>160.4</v>
       </c>
       <c r="G26">
-        <v>142.26</v>
+        <v>110.36</v>
       </c>
       <c r="H26">
-        <v>107.7</v>
+        <v>73.4</v>
       </c>
       <c r="I26">
-        <v>278.6</v>
+        <v>217.2</v>
       </c>
       <c r="J26">
-        <v>156.6</v>
+        <v>127.2</v>
       </c>
       <c r="K26">
-        <v>15959</v>
+        <v>10823</v>
       </c>
       <c r="L26">
-        <v>5233.44</v>
+        <v>3434.28</v>
       </c>
       <c r="M26">
-        <v>6.26</v>
+        <v>46.04</v>
       </c>
       <c r="N26">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="O26">
-        <v>4.95</v>
+        <v>57.32</v>
       </c>
       <c r="P26">
-        <v>80.5</v>
+        <v>72.67</v>
       </c>
       <c r="Q26">
-        <v>0.76</v>
+        <v>66.35</v>
       </c>
       <c r="R26">
-        <v>11.3</v>
+        <v>56.6</v>
       </c>
       <c r="S26">
-        <v>26772.16</v>
+        <v>20100.99</v>
       </c>
       <c r="T26">
-        <v>1747.29</v>
+        <v>11658.76</v>
       </c>
       <c r="U26">
-        <v>1456.08</v>
+        <v>9715.68</v>
       </c>
       <c r="V26">
-        <v>18</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
@@ -2320,64 +2320,64 @@
         <v>36</v>
       </c>
       <c r="C27">
-        <v>3455.36</v>
+        <v>3938.35</v>
       </c>
       <c r="D27">
-        <v>414.64</v>
+        <v>472.6</v>
       </c>
       <c r="E27">
-        <v>549.39</v>
+        <v>409.82</v>
       </c>
       <c r="F27">
-        <v>243.7</v>
+        <v>160.4</v>
       </c>
       <c r="G27">
-        <v>142.26</v>
+        <v>110.36</v>
       </c>
       <c r="H27">
-        <v>107.7</v>
+        <v>73.4</v>
       </c>
       <c r="I27">
-        <v>278.6</v>
+        <v>217.2</v>
       </c>
       <c r="J27">
-        <v>156.6</v>
+        <v>127.2</v>
       </c>
       <c r="K27">
-        <v>15959</v>
+        <v>10823</v>
       </c>
       <c r="L27">
-        <v>5233.44</v>
+        <v>3434.28</v>
       </c>
       <c r="M27">
-        <v>9.95</v>
+        <v>43.55</v>
       </c>
       <c r="N27">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="O27">
-        <v>7.87</v>
+        <v>54.22</v>
       </c>
       <c r="P27">
-        <v>80.5</v>
+        <v>72.67</v>
       </c>
       <c r="Q27">
-        <v>1.37</v>
+        <v>55.7</v>
       </c>
       <c r="R27">
-        <v>38.9</v>
+        <v>153.6</v>
       </c>
       <c r="S27">
-        <v>26779.38</v>
+        <v>20084.75</v>
       </c>
       <c r="T27">
-        <v>2778.62</v>
+        <v>11027.93</v>
       </c>
       <c r="U27">
-        <v>2315.53</v>
+        <v>9189.97</v>
       </c>
       <c r="V27">
-        <v>28</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
@@ -2388,64 +2388,64 @@
         <v>36</v>
       </c>
       <c r="C28">
-        <v>3455.36</v>
+        <v>3938.35</v>
       </c>
       <c r="D28">
-        <v>414.64</v>
+        <v>472.6</v>
       </c>
       <c r="E28">
-        <v>481.92</v>
+        <v>359.49</v>
       </c>
       <c r="F28">
-        <v>243.7</v>
+        <v>160.4</v>
       </c>
       <c r="G28">
-        <v>142.26</v>
+        <v>110.36</v>
       </c>
       <c r="H28">
-        <v>107.7</v>
+        <v>73.4</v>
       </c>
       <c r="I28">
-        <v>278.6</v>
+        <v>217.2</v>
       </c>
       <c r="J28">
-        <v>156.6</v>
+        <v>127.2</v>
       </c>
       <c r="K28">
-        <v>15959</v>
+        <v>10823</v>
       </c>
       <c r="L28">
-        <v>5233.44</v>
+        <v>3434.28</v>
       </c>
       <c r="M28">
-        <v>5.82</v>
+        <v>50.9</v>
       </c>
       <c r="N28">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="O28">
-        <v>4.6</v>
+        <v>63.37</v>
       </c>
       <c r="P28">
-        <v>80.5</v>
+        <v>72.67</v>
       </c>
       <c r="Q28">
-        <v>1.02</v>
+        <v>77.79</v>
       </c>
       <c r="R28">
-        <v>55.4</v>
+        <v>122</v>
       </c>
       <c r="S28">
-        <v>26704.16</v>
+        <v>20073.01</v>
       </c>
       <c r="T28">
-        <v>1624.85</v>
+        <v>12888.53</v>
       </c>
       <c r="U28">
-        <v>1354.04</v>
+        <v>10740.4</v>
       </c>
       <c r="V28">
-        <v>18</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.25">
@@ -2456,64 +2456,64 @@
         <v>36</v>
       </c>
       <c r="C29">
-        <v>3455.36</v>
+        <v>3938.35</v>
       </c>
       <c r="D29">
-        <v>414.64</v>
+        <v>472.6</v>
       </c>
       <c r="E29">
-        <v>481.92</v>
+        <v>359.49</v>
       </c>
       <c r="F29">
-        <v>243.7</v>
+        <v>160.4</v>
       </c>
       <c r="G29">
-        <v>142.26</v>
+        <v>110.36</v>
       </c>
       <c r="H29">
-        <v>107.7</v>
+        <v>73.4</v>
       </c>
       <c r="I29">
-        <v>278.6</v>
+        <v>217.2</v>
       </c>
       <c r="J29">
-        <v>156.6</v>
+        <v>127.2</v>
       </c>
       <c r="K29">
-        <v>15959</v>
+        <v>10823</v>
       </c>
       <c r="L29">
-        <v>5233.44</v>
+        <v>3434.28</v>
       </c>
       <c r="M29">
-        <v>5.97</v>
+        <v>58.02</v>
       </c>
       <c r="N29">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="O29">
-        <v>4.72</v>
+        <v>72.23</v>
       </c>
       <c r="P29">
-        <v>80.5</v>
+        <v>72.67</v>
       </c>
       <c r="Q29">
-        <v>0.78</v>
+        <v>86.23</v>
       </c>
       <c r="R29">
-        <v>48.1</v>
+        <v>207.8</v>
       </c>
       <c r="S29">
-        <v>26704.19</v>
+        <v>20097.43</v>
       </c>
       <c r="T29">
-        <v>1667.16</v>
+        <v>14691.6</v>
       </c>
       <c r="U29">
-        <v>1389.31</v>
+        <v>12243.08</v>
       </c>
       <c r="V29">
-        <v>19</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
@@ -2524,64 +2524,64 @@
         <v>36</v>
       </c>
       <c r="C30">
-        <v>3455.36</v>
+        <v>3938.35</v>
       </c>
       <c r="D30">
-        <v>414.64</v>
+        <v>472.6</v>
       </c>
       <c r="E30">
-        <v>481.92</v>
+        <v>359.49</v>
       </c>
       <c r="F30">
-        <v>243.7</v>
+        <v>160.4</v>
       </c>
       <c r="G30">
-        <v>142.26</v>
+        <v>110.36</v>
       </c>
       <c r="H30">
-        <v>107.7</v>
+        <v>73.4</v>
       </c>
       <c r="I30">
-        <v>278.6</v>
+        <v>217.2</v>
       </c>
       <c r="J30">
-        <v>156.6</v>
+        <v>127.2</v>
       </c>
       <c r="K30">
-        <v>15959</v>
+        <v>10823</v>
       </c>
       <c r="L30">
-        <v>5233.44</v>
+        <v>3434.28</v>
       </c>
       <c r="M30">
-        <v>4.85</v>
+        <v>53.77</v>
       </c>
       <c r="N30">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="O30">
-        <v>3.83</v>
+        <v>66.94</v>
       </c>
       <c r="P30">
-        <v>80.5</v>
+        <v>72.67</v>
       </c>
       <c r="Q30">
-        <v>0.68</v>
+        <v>81.22</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>65.9</v>
       </c>
       <c r="S30">
-        <v>26702.08</v>
+        <v>20082.88</v>
       </c>
       <c r="T30">
-        <v>1353.41</v>
+        <v>13615.35</v>
       </c>
       <c r="U30">
-        <v>1127.85</v>
+        <v>11346.22</v>
       </c>
       <c r="V30">
-        <v>16</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
@@ -2592,64 +2592,64 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>3455.36</v>
+        <v>3938.35</v>
       </c>
       <c r="D31">
-        <v>414.64</v>
+        <v>472.6</v>
       </c>
       <c r="E31">
-        <v>520.47</v>
+        <v>388.25</v>
       </c>
       <c r="F31">
-        <v>243.7</v>
+        <v>160.4</v>
       </c>
       <c r="G31">
-        <v>142.26</v>
+        <v>110.36</v>
       </c>
       <c r="H31">
-        <v>107.7</v>
+        <v>73.4</v>
       </c>
       <c r="I31">
-        <v>278.6</v>
+        <v>217.2</v>
       </c>
       <c r="J31">
-        <v>156.6</v>
+        <v>127.2</v>
       </c>
       <c r="K31">
-        <v>15959</v>
+        <v>10823</v>
       </c>
       <c r="L31">
-        <v>5233.44</v>
+        <v>3434.28</v>
       </c>
       <c r="M31">
-        <v>7.59</v>
+        <v>49.24</v>
       </c>
       <c r="N31">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="O31">
-        <v>6</v>
+        <v>61.31</v>
       </c>
       <c r="P31">
-        <v>80.5</v>
+        <v>72.67</v>
       </c>
       <c r="Q31">
-        <v>1.12</v>
+        <v>65.21</v>
       </c>
       <c r="R31">
-        <v>15</v>
+        <v>81.8</v>
       </c>
       <c r="S31">
-        <v>26745.98</v>
+        <v>20085.47</v>
       </c>
       <c r="T31">
-        <v>2118.27</v>
+        <v>12469.19</v>
       </c>
       <c r="U31">
-        <v>1765.21</v>
+        <v>10391</v>
       </c>
       <c r="V31">
-        <v>21</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
@@ -2660,64 +2660,64 @@
         <v>36</v>
       </c>
       <c r="C32">
-        <v>3455.36</v>
+        <v>3938.35</v>
       </c>
       <c r="D32">
-        <v>414.64</v>
+        <v>472.6</v>
       </c>
       <c r="E32">
-        <v>520.47</v>
+        <v>388.25</v>
       </c>
       <c r="F32">
-        <v>243.7</v>
+        <v>160.4</v>
       </c>
       <c r="G32">
-        <v>142.26</v>
+        <v>110.36</v>
       </c>
       <c r="H32">
-        <v>107.7</v>
+        <v>73.4</v>
       </c>
       <c r="I32">
-        <v>278.6</v>
+        <v>217.2</v>
       </c>
       <c r="J32">
-        <v>156.6</v>
+        <v>127.2</v>
       </c>
       <c r="K32">
-        <v>15959</v>
+        <v>10823</v>
       </c>
       <c r="L32">
-        <v>5233.44</v>
+        <v>3434.28</v>
       </c>
       <c r="M32">
-        <v>6.87</v>
+        <v>47.14</v>
       </c>
       <c r="N32">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="O32">
-        <v>5.44</v>
+        <v>58.69</v>
       </c>
       <c r="P32">
-        <v>80.5</v>
+        <v>72.67</v>
       </c>
       <c r="Q32">
-        <v>0.69</v>
+        <v>67.14</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="S32">
-        <v>26744.27</v>
+        <v>20082.68</v>
       </c>
       <c r="T32">
-        <v>1918.9</v>
+        <v>11937.26</v>
       </c>
       <c r="U32">
-        <v>1599.11</v>
+        <v>9947.77</v>
       </c>
       <c r="V32">
-        <v>20</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
@@ -2728,64 +2728,64 @@
         <v>36</v>
       </c>
       <c r="C33">
-        <v>3455.36</v>
+        <v>3938.35</v>
       </c>
       <c r="D33">
-        <v>414.64</v>
+        <v>472.6</v>
       </c>
       <c r="E33">
-        <v>520.47</v>
+        <v>388.25</v>
       </c>
       <c r="F33">
-        <v>243.7</v>
+        <v>160.4</v>
       </c>
       <c r="G33">
-        <v>142.26</v>
+        <v>110.36</v>
       </c>
       <c r="H33">
-        <v>107.7</v>
+        <v>73.4</v>
       </c>
       <c r="I33">
-        <v>278.6</v>
+        <v>217.2</v>
       </c>
       <c r="J33">
-        <v>156.6</v>
+        <v>127.2</v>
       </c>
       <c r="K33">
-        <v>15959</v>
+        <v>10823</v>
       </c>
       <c r="L33">
-        <v>5233.44</v>
+        <v>3434.28</v>
       </c>
       <c r="M33">
-        <v>8</v>
+        <v>52.49</v>
       </c>
       <c r="N33">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="O33">
-        <v>6.32</v>
+        <v>65.35</v>
       </c>
       <c r="P33">
-        <v>80.5</v>
+        <v>72.67</v>
       </c>
       <c r="Q33">
-        <v>0.92</v>
+        <v>74.22</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>142.3</v>
       </c>
       <c r="S33">
-        <v>26746.51</v>
+        <v>20101.77</v>
       </c>
       <c r="T33">
-        <v>2232.15</v>
+        <v>13292.47</v>
       </c>
       <c r="U33">
-        <v>1860.13</v>
+        <v>11077.09</v>
       </c>
       <c r="V33">
-        <v>23</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
@@ -2796,64 +2796,64 @@
         <v>36</v>
       </c>
       <c r="C34">
-        <v>3455.36</v>
+        <v>3938.35</v>
       </c>
       <c r="D34">
-        <v>414.64</v>
+        <v>472.6</v>
       </c>
       <c r="E34">
-        <v>481.92</v>
+        <v>359.49</v>
       </c>
       <c r="F34">
-        <v>243.7</v>
+        <v>160.4</v>
       </c>
       <c r="G34">
-        <v>142.26</v>
+        <v>110.36</v>
       </c>
       <c r="H34">
-        <v>107.7</v>
+        <v>73.4</v>
       </c>
       <c r="I34">
-        <v>278.6</v>
+        <v>217.2</v>
       </c>
       <c r="J34">
-        <v>156.6</v>
+        <v>127.2</v>
       </c>
       <c r="K34">
-        <v>15959</v>
+        <v>10823</v>
       </c>
       <c r="L34">
-        <v>5233.44</v>
+        <v>3434.28</v>
       </c>
       <c r="M34">
-        <v>7.2</v>
+        <v>50.32</v>
       </c>
       <c r="N34">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="O34">
-        <v>5.7</v>
+        <v>62.65</v>
       </c>
       <c r="P34">
-        <v>80.5</v>
+        <v>72.67</v>
       </c>
       <c r="Q34">
-        <v>0.98</v>
+        <v>72.29</v>
       </c>
       <c r="R34">
-        <v>85.5</v>
+        <v>272.5</v>
       </c>
       <c r="S34">
-        <v>26706.6</v>
+        <v>20066.21</v>
       </c>
       <c r="T34">
-        <v>2011.34</v>
+        <v>12741.76</v>
       </c>
       <c r="U34">
-        <v>1676.1</v>
+        <v>10618.15</v>
       </c>
       <c r="V34">
-        <v>23</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
@@ -2864,64 +2864,64 @@
         <v>36</v>
       </c>
       <c r="C35">
-        <v>3455.36</v>
+        <v>3938.35</v>
       </c>
       <c r="D35">
-        <v>414.64</v>
+        <v>472.6</v>
       </c>
       <c r="E35">
-        <v>481.92</v>
+        <v>359.49</v>
       </c>
       <c r="F35">
-        <v>243.7</v>
+        <v>160.4</v>
       </c>
       <c r="G35">
-        <v>142.26</v>
+        <v>110.36</v>
       </c>
       <c r="H35">
-        <v>107.7</v>
+        <v>73.4</v>
       </c>
       <c r="I35">
-        <v>278.6</v>
+        <v>217.2</v>
       </c>
       <c r="J35">
-        <v>156.6</v>
+        <v>127.2</v>
       </c>
       <c r="K35">
-        <v>15959</v>
+        <v>10823</v>
       </c>
       <c r="L35">
-        <v>5233.44</v>
+        <v>3434.28</v>
       </c>
       <c r="M35">
-        <v>8.62</v>
+        <v>67.97</v>
       </c>
       <c r="N35">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="O35">
-        <v>6.82</v>
+        <v>84.62</v>
       </c>
       <c r="P35">
-        <v>80.5</v>
+        <v>72.67</v>
       </c>
       <c r="Q35">
-        <v>1.07</v>
+        <v>96.24</v>
       </c>
       <c r="R35">
-        <v>23.7</v>
+        <v>60.2</v>
       </c>
       <c r="S35">
-        <v>26709.23</v>
+        <v>20129.78</v>
       </c>
       <c r="T35">
-        <v>2406.13</v>
+        <v>17211.66</v>
       </c>
       <c r="U35">
-        <v>2005.13</v>
+        <v>14343.15</v>
       </c>
       <c r="V35">
-        <v>26</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
@@ -2932,64 +2932,64 @@
         <v>36</v>
       </c>
       <c r="C36">
-        <v>3455.36</v>
+        <v>3938.35</v>
       </c>
       <c r="D36">
-        <v>414.64</v>
+        <v>472.6</v>
       </c>
       <c r="E36">
-        <v>481.92</v>
+        <v>359.49</v>
       </c>
       <c r="F36">
-        <v>243.7</v>
+        <v>160.4</v>
       </c>
       <c r="G36">
-        <v>142.26</v>
+        <v>110.36</v>
       </c>
       <c r="H36">
-        <v>107.7</v>
+        <v>73.4</v>
       </c>
       <c r="I36">
-        <v>278.6</v>
+        <v>217.2</v>
       </c>
       <c r="J36">
-        <v>156.6</v>
+        <v>127.2</v>
       </c>
       <c r="K36">
-        <v>15959</v>
+        <v>10823</v>
       </c>
       <c r="L36">
-        <v>5233.44</v>
+        <v>3434.28</v>
       </c>
       <c r="M36">
-        <v>10.7</v>
+        <v>68.79</v>
       </c>
       <c r="N36">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="O36">
-        <v>8.46</v>
+        <v>85.65</v>
       </c>
       <c r="P36">
-        <v>80.5</v>
+        <v>72.67</v>
       </c>
       <c r="Q36">
-        <v>1.51</v>
+        <v>90.09</v>
       </c>
       <c r="R36">
-        <v>41.1</v>
+        <v>118</v>
       </c>
       <c r="S36">
-        <v>26713.39</v>
+        <v>20125.48</v>
       </c>
       <c r="T36">
-        <v>2986.29</v>
+        <v>17419.49</v>
       </c>
       <c r="U36">
-        <v>2488.58</v>
+        <v>14516.26</v>
       </c>
       <c r="V36">
-        <v>31</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
@@ -3000,64 +3000,64 @@
         <v>36</v>
       </c>
       <c r="C37">
-        <v>3455.36</v>
+        <v>3938.35</v>
       </c>
       <c r="D37">
-        <v>414.64</v>
+        <v>472.6</v>
       </c>
       <c r="E37">
-        <v>549.39</v>
+        <v>409.82</v>
       </c>
       <c r="F37">
-        <v>243.7</v>
+        <v>160.4</v>
       </c>
       <c r="G37">
-        <v>142.26</v>
+        <v>110.36</v>
       </c>
       <c r="H37">
-        <v>107.7</v>
+        <v>73.4</v>
       </c>
       <c r="I37">
-        <v>278.6</v>
+        <v>217.2</v>
       </c>
       <c r="J37">
-        <v>156.6</v>
+        <v>127.2</v>
       </c>
       <c r="K37">
-        <v>15959</v>
+        <v>10823</v>
       </c>
       <c r="L37">
-        <v>5233.44</v>
+        <v>3434.28</v>
       </c>
       <c r="M37">
-        <v>11.06</v>
+        <v>76.54</v>
       </c>
       <c r="N37">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="O37">
-        <v>8.75</v>
+        <v>95.29</v>
       </c>
       <c r="P37">
-        <v>80.5</v>
+        <v>72.67</v>
       </c>
       <c r="Q37">
-        <v>1.66</v>
+        <v>104.39</v>
       </c>
       <c r="R37">
-        <v>16.4</v>
+        <v>129.8</v>
       </c>
       <c r="S37">
-        <v>26781.66</v>
+        <v>20207.5</v>
       </c>
       <c r="T37">
-        <v>3086.7</v>
+        <v>19381.46</v>
       </c>
       <c r="U37">
-        <v>2572.26</v>
+        <v>16151.24</v>
       </c>
       <c r="V37">
-        <v>34</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
@@ -3068,64 +3068,64 @@
         <v>37</v>
       </c>
       <c r="C38">
-        <v>3089.9</v>
+        <v>2924.01</v>
       </c>
       <c r="D38">
-        <v>370.79</v>
+        <v>350.88</v>
       </c>
       <c r="E38">
-        <v>432.39</v>
+        <v>423.91</v>
       </c>
       <c r="F38">
-        <v>151.9</v>
+        <v>160.06</v>
       </c>
       <c r="G38">
-        <v>103.25</v>
+        <v>106.05</v>
       </c>
       <c r="H38">
-        <v>63.25</v>
+        <v>66.05</v>
       </c>
       <c r="I38">
-        <v>208.5</v>
+        <v>210.9</v>
       </c>
       <c r="J38">
-        <v>118.5</v>
+        <v>120.9</v>
       </c>
       <c r="K38">
-        <v>11294</v>
+        <v>13511</v>
       </c>
       <c r="L38">
-        <v>3326.22</v>
+        <v>4281.78</v>
       </c>
       <c r="M38">
-        <v>3.91</v>
+        <v>110.31</v>
       </c>
       <c r="N38">
-        <v>158</v>
+        <v>161.61</v>
       </c>
       <c r="O38">
-        <v>4.23</v>
+        <v>113.13</v>
       </c>
       <c r="P38">
-        <v>72.08</v>
+        <v>74.08</v>
       </c>
       <c r="Q38">
-        <v>0.51</v>
+        <v>159.49</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>158.8</v>
       </c>
       <c r="S38">
-        <v>19397.43</v>
+        <v>22774.16</v>
       </c>
       <c r="T38">
-        <v>875.72</v>
+        <v>27705.04</v>
       </c>
       <c r="U38">
-        <v>729.79</v>
+        <v>23087.44</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
@@ -3136,64 +3136,64 @@
         <v>37</v>
       </c>
       <c r="C39">
-        <v>3089.9</v>
+        <v>2924.01</v>
       </c>
       <c r="D39">
-        <v>370.79</v>
+        <v>350.88</v>
       </c>
       <c r="E39">
-        <v>432.39</v>
+        <v>423.91</v>
       </c>
       <c r="F39">
-        <v>151.9</v>
+        <v>160.06</v>
       </c>
       <c r="G39">
-        <v>103.25</v>
+        <v>106.05</v>
       </c>
       <c r="H39">
-        <v>63.25</v>
+        <v>66.05</v>
       </c>
       <c r="I39">
-        <v>208.5</v>
+        <v>210.9</v>
       </c>
       <c r="J39">
-        <v>118.5</v>
+        <v>120.9</v>
       </c>
       <c r="K39">
-        <v>11294</v>
+        <v>13511</v>
       </c>
       <c r="L39">
-        <v>3326.22</v>
+        <v>4281.78</v>
       </c>
       <c r="M39">
-        <v>8.25</v>
+        <v>117.05</v>
       </c>
       <c r="N39">
-        <v>158</v>
+        <v>171.49</v>
       </c>
       <c r="O39">
-        <v>8.93</v>
+        <v>120.04</v>
       </c>
       <c r="P39">
-        <v>72.08</v>
+        <v>74.08</v>
       </c>
       <c r="Q39">
-        <v>1</v>
+        <v>167.85</v>
       </c>
       <c r="R39">
-        <v>13.6</v>
+        <v>228</v>
       </c>
       <c r="S39">
-        <v>19406.96</v>
+        <v>22806.05</v>
       </c>
       <c r="T39">
-        <v>1846.62</v>
+        <v>29397.73</v>
       </c>
       <c r="U39">
-        <v>1538.85</v>
+        <v>24497.98</v>
       </c>
       <c r="V39">
-        <v>15</v>
+        <v>235</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
@@ -3204,64 +3204,64 @@
         <v>37</v>
       </c>
       <c r="C40">
-        <v>3089.9</v>
+        <v>2924.01</v>
       </c>
       <c r="D40">
-        <v>370.79</v>
+        <v>350.88</v>
       </c>
       <c r="E40">
-        <v>379.29</v>
+        <v>371.86</v>
       </c>
       <c r="F40">
-        <v>151.9</v>
+        <v>160.06</v>
       </c>
       <c r="G40">
-        <v>103.25</v>
+        <v>106.05</v>
       </c>
       <c r="H40">
-        <v>63.25</v>
+        <v>66.05</v>
       </c>
       <c r="I40">
-        <v>208.5</v>
+        <v>210.9</v>
       </c>
       <c r="J40">
-        <v>118.5</v>
+        <v>120.9</v>
       </c>
       <c r="K40">
-        <v>11294</v>
+        <v>13511</v>
       </c>
       <c r="L40">
-        <v>3326.22</v>
+        <v>4281.78</v>
       </c>
       <c r="M40">
-        <v>8.48</v>
+        <v>121.93</v>
       </c>
       <c r="N40">
-        <v>158</v>
+        <v>178.64</v>
       </c>
       <c r="O40">
-        <v>9.17</v>
+        <v>125.05</v>
       </c>
       <c r="P40">
-        <v>72.08</v>
+        <v>74.08</v>
       </c>
       <c r="Q40">
-        <v>0.73</v>
+        <v>179.71</v>
       </c>
       <c r="R40">
-        <v>10.2</v>
+        <v>119</v>
       </c>
       <c r="S40">
-        <v>19354.06</v>
+        <v>22782.9</v>
       </c>
       <c r="T40">
-        <v>1897.89</v>
+        <v>30624.12</v>
       </c>
       <c r="U40">
-        <v>1581.58</v>
+        <v>25519.98</v>
       </c>
       <c r="V40">
-        <v>18</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
@@ -3272,64 +3272,64 @@
         <v>37</v>
       </c>
       <c r="C41">
-        <v>3089.9</v>
+        <v>2924.01</v>
       </c>
       <c r="D41">
-        <v>370.79</v>
+        <v>350.88</v>
       </c>
       <c r="E41">
-        <v>379.29</v>
+        <v>371.86</v>
       </c>
       <c r="F41">
-        <v>151.9</v>
+        <v>160.06</v>
       </c>
       <c r="G41">
-        <v>103.25</v>
+        <v>106.05</v>
       </c>
       <c r="H41">
-        <v>63.25</v>
+        <v>66.05</v>
       </c>
       <c r="I41">
-        <v>208.5</v>
+        <v>210.9</v>
       </c>
       <c r="J41">
-        <v>118.5</v>
+        <v>120.9</v>
       </c>
       <c r="K41">
-        <v>11294</v>
+        <v>13511</v>
       </c>
       <c r="L41">
-        <v>3326.22</v>
+        <v>4281.78</v>
       </c>
       <c r="M41">
-        <v>9.71</v>
+        <v>134.92</v>
       </c>
       <c r="N41">
-        <v>158</v>
+        <v>197.67</v>
       </c>
       <c r="O41">
-        <v>10.51</v>
+        <v>138.37</v>
       </c>
       <c r="P41">
-        <v>72.08</v>
+        <v>74.08</v>
       </c>
       <c r="Q41">
-        <v>1.21</v>
+        <v>194.86</v>
       </c>
       <c r="R41">
-        <v>19.2</v>
+        <v>256.2</v>
       </c>
       <c r="S41">
-        <v>19357.11</v>
+        <v>22843.39</v>
       </c>
       <c r="T41">
-        <v>2174.13</v>
+        <v>33886.16</v>
       </c>
       <c r="U41">
-        <v>1811.78</v>
+        <v>28238.41</v>
       </c>
       <c r="V41">
-        <v>20</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
@@ -3340,64 +3340,64 @@
         <v>37</v>
       </c>
       <c r="C42">
-        <v>3089.9</v>
+        <v>2924.01</v>
       </c>
       <c r="D42">
-        <v>370.79</v>
+        <v>350.88</v>
       </c>
       <c r="E42">
-        <v>379.29</v>
+        <v>371.86</v>
       </c>
       <c r="F42">
-        <v>151.9</v>
+        <v>160.06</v>
       </c>
       <c r="G42">
-        <v>103.25</v>
+        <v>106.05</v>
       </c>
       <c r="H42">
-        <v>63.25</v>
+        <v>66.05</v>
       </c>
       <c r="I42">
-        <v>208.5</v>
+        <v>210.9</v>
       </c>
       <c r="J42">
-        <v>118.5</v>
+        <v>120.9</v>
       </c>
       <c r="K42">
-        <v>11294</v>
+        <v>13511</v>
       </c>
       <c r="L42">
-        <v>3326.22</v>
+        <v>4281.78</v>
       </c>
       <c r="M42">
-        <v>10.91</v>
+        <v>130.52</v>
       </c>
       <c r="N42">
-        <v>158</v>
+        <v>191.22</v>
       </c>
       <c r="O42">
-        <v>11.8</v>
+        <v>133.85</v>
       </c>
       <c r="P42">
-        <v>72.08</v>
+        <v>74.08</v>
       </c>
       <c r="Q42">
-        <v>1.22</v>
+        <v>198.81</v>
       </c>
       <c r="R42">
-        <v>23.2</v>
+        <v>228.5</v>
       </c>
       <c r="S42">
-        <v>19359.61</v>
+        <v>22831.97</v>
       </c>
       <c r="T42">
-        <v>2441.03</v>
+        <v>32780.65</v>
       </c>
       <c r="U42">
-        <v>2034.21</v>
+        <v>27317.07</v>
       </c>
       <c r="V42">
-        <v>18</v>
+        <v>275</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
@@ -3408,64 +3408,64 @@
         <v>37</v>
       </c>
       <c r="C43">
-        <v>3089.9</v>
+        <v>2924.01</v>
       </c>
       <c r="D43">
-        <v>370.79</v>
+        <v>350.88</v>
       </c>
       <c r="E43">
-        <v>409.63</v>
+        <v>401.6</v>
       </c>
       <c r="F43">
-        <v>151.9</v>
+        <v>160.06</v>
       </c>
       <c r="G43">
-        <v>103.25</v>
+        <v>106.05</v>
       </c>
       <c r="H43">
-        <v>63.25</v>
+        <v>66.05</v>
       </c>
       <c r="I43">
-        <v>208.5</v>
+        <v>210.9</v>
       </c>
       <c r="J43">
-        <v>118.5</v>
+        <v>120.9</v>
       </c>
       <c r="K43">
-        <v>11294</v>
+        <v>13511</v>
       </c>
       <c r="L43">
-        <v>3326.22</v>
+        <v>4281.78</v>
       </c>
       <c r="M43">
-        <v>6.33</v>
+        <v>111.53</v>
       </c>
       <c r="N43">
-        <v>158</v>
+        <v>163.4</v>
       </c>
       <c r="O43">
-        <v>6.85</v>
+        <v>114.38</v>
       </c>
       <c r="P43">
-        <v>72.08</v>
+        <v>74.08</v>
       </c>
       <c r="Q43">
-        <v>0.77</v>
+        <v>173.15</v>
       </c>
       <c r="R43">
-        <v>37.3</v>
+        <v>288.1</v>
       </c>
       <c r="S43">
-        <v>19379.97</v>
+        <v>22769.77</v>
       </c>
       <c r="T43">
-        <v>1417.9</v>
+        <v>28012</v>
       </c>
       <c r="U43">
-        <v>1181.59</v>
+        <v>23343.27</v>
       </c>
       <c r="V43">
-        <v>14</v>
+        <v>260</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -3476,64 +3476,64 @@
         <v>37</v>
       </c>
       <c r="C44">
-        <v>3089.9</v>
+        <v>2924.01</v>
       </c>
       <c r="D44">
-        <v>370.79</v>
+        <v>350.88</v>
       </c>
       <c r="E44">
-        <v>409.63</v>
+        <v>401.6</v>
       </c>
       <c r="F44">
-        <v>151.9</v>
+        <v>160.06</v>
       </c>
       <c r="G44">
-        <v>103.25</v>
+        <v>106.05</v>
       </c>
       <c r="H44">
-        <v>63.25</v>
+        <v>66.05</v>
       </c>
       <c r="I44">
-        <v>208.5</v>
+        <v>210.9</v>
       </c>
       <c r="J44">
-        <v>118.5</v>
+        <v>120.9</v>
       </c>
       <c r="K44">
-        <v>11294</v>
+        <v>13511</v>
       </c>
       <c r="L44">
-        <v>3326.22</v>
+        <v>4281.78</v>
       </c>
       <c r="M44">
-        <v>5.07</v>
+        <v>113.73</v>
       </c>
       <c r="N44">
-        <v>158</v>
+        <v>166.62</v>
       </c>
       <c r="O44">
-        <v>5.48</v>
+        <v>116.64</v>
       </c>
       <c r="P44">
-        <v>72.08</v>
+        <v>74.08</v>
       </c>
       <c r="Q44">
-        <v>0.54</v>
+        <v>169.64</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>279.2</v>
       </c>
       <c r="S44">
-        <v>19377.11</v>
+        <v>22773.94</v>
       </c>
       <c r="T44">
-        <v>1134.05</v>
+        <v>28564.09</v>
       </c>
       <c r="U44">
-        <v>945.05</v>
+        <v>23803.26</v>
       </c>
       <c r="V44">
-        <v>7</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
@@ -3544,64 +3544,64 @@
         <v>37</v>
       </c>
       <c r="C45">
-        <v>3089.9</v>
+        <v>2924.01</v>
       </c>
       <c r="D45">
-        <v>370.79</v>
+        <v>350.88</v>
       </c>
       <c r="E45">
-        <v>409.63</v>
+        <v>401.6</v>
       </c>
       <c r="F45">
-        <v>151.9</v>
+        <v>160.06</v>
       </c>
       <c r="G45">
-        <v>103.25</v>
+        <v>106.05</v>
       </c>
       <c r="H45">
-        <v>63.25</v>
+        <v>66.05</v>
       </c>
       <c r="I45">
-        <v>208.5</v>
+        <v>210.9</v>
       </c>
       <c r="J45">
-        <v>118.5</v>
+        <v>120.9</v>
       </c>
       <c r="K45">
-        <v>11294</v>
+        <v>13511</v>
       </c>
       <c r="L45">
-        <v>3326.22</v>
+        <v>4281.78</v>
       </c>
       <c r="M45">
-        <v>6.14</v>
+        <v>129.18</v>
       </c>
       <c r="N45">
-        <v>158</v>
+        <v>189.26</v>
       </c>
       <c r="O45">
-        <v>6.64</v>
+        <v>132.48</v>
       </c>
       <c r="P45">
-        <v>72.08</v>
+        <v>74.08</v>
       </c>
       <c r="Q45">
-        <v>0.71</v>
+        <v>188.96</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>272.8</v>
       </c>
       <c r="S45">
-        <v>19379.51</v>
+        <v>22847.19</v>
       </c>
       <c r="T45">
-        <v>1374.71</v>
+        <v>32444.22</v>
       </c>
       <c r="U45">
-        <v>1145.6</v>
+        <v>27036.77</v>
       </c>
       <c r="V45">
-        <v>10</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
@@ -3612,64 +3612,64 @@
         <v>37</v>
       </c>
       <c r="C46">
-        <v>3089.9</v>
+        <v>2924.01</v>
       </c>
       <c r="D46">
-        <v>370.79</v>
+        <v>350.88</v>
       </c>
       <c r="E46">
-        <v>379.29</v>
+        <v>371.86</v>
       </c>
       <c r="F46">
-        <v>151.9</v>
+        <v>160.06</v>
       </c>
       <c r="G46">
-        <v>103.25</v>
+        <v>106.05</v>
       </c>
       <c r="H46">
-        <v>63.25</v>
+        <v>66.05</v>
       </c>
       <c r="I46">
-        <v>208.5</v>
+        <v>210.9</v>
       </c>
       <c r="J46">
-        <v>118.5</v>
+        <v>120.9</v>
       </c>
       <c r="K46">
-        <v>11294</v>
+        <v>13511</v>
       </c>
       <c r="L46">
-        <v>3326.22</v>
+        <v>4281.78</v>
       </c>
       <c r="M46">
-        <v>10.75</v>
+        <v>139.92</v>
       </c>
       <c r="N46">
-        <v>158</v>
+        <v>204.99</v>
       </c>
       <c r="O46">
-        <v>11.63</v>
+        <v>143.49</v>
       </c>
       <c r="P46">
-        <v>72.08</v>
+        <v>74.08</v>
       </c>
       <c r="Q46">
-        <v>1.4</v>
+        <v>203.66</v>
       </c>
       <c r="R46">
-        <v>45.3</v>
+        <v>406.8</v>
       </c>
       <c r="S46">
-        <v>19359.46</v>
+        <v>22869.63</v>
       </c>
       <c r="T46">
-        <v>2405.79</v>
+        <v>35140.98</v>
       </c>
       <c r="U46">
-        <v>2004.84</v>
+        <v>29284.1</v>
       </c>
       <c r="V46">
-        <v>16</v>
+        <v>296</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
@@ -3680,64 +3680,64 @@
         <v>37</v>
       </c>
       <c r="C47">
-        <v>3089.9</v>
+        <v>2924.01</v>
       </c>
       <c r="D47">
-        <v>370.79</v>
+        <v>350.88</v>
       </c>
       <c r="E47">
-        <v>379.29</v>
+        <v>371.86</v>
       </c>
       <c r="F47">
-        <v>151.9</v>
+        <v>160.06</v>
       </c>
       <c r="G47">
-        <v>103.25</v>
+        <v>106.05</v>
       </c>
       <c r="H47">
-        <v>63.25</v>
+        <v>66.05</v>
       </c>
       <c r="I47">
-        <v>208.5</v>
+        <v>210.9</v>
       </c>
       <c r="J47">
-        <v>118.5</v>
+        <v>120.9</v>
       </c>
       <c r="K47">
-        <v>11294</v>
+        <v>13511</v>
       </c>
       <c r="L47">
-        <v>3326.22</v>
+        <v>4281.78</v>
       </c>
       <c r="M47">
-        <v>5.61</v>
+        <v>143.73</v>
       </c>
       <c r="N47">
-        <v>158</v>
+        <v>210.58</v>
       </c>
       <c r="O47">
-        <v>6.06</v>
+        <v>147.41</v>
       </c>
       <c r="P47">
-        <v>72.08</v>
+        <v>74.08</v>
       </c>
       <c r="Q47">
-        <v>0.71</v>
+        <v>207.76</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>193.7</v>
       </c>
       <c r="S47">
-        <v>19348.06</v>
+        <v>22887.05</v>
       </c>
       <c r="T47">
-        <v>1254.8</v>
+        <v>36099.7</v>
       </c>
       <c r="U47">
-        <v>1045.68</v>
+        <v>30082.88</v>
       </c>
       <c r="V47">
-        <v>12</v>
+        <v>323</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
@@ -3748,64 +3748,64 @@
         <v>37</v>
       </c>
       <c r="C48">
-        <v>3089.9</v>
+        <v>2924.01</v>
       </c>
       <c r="D48">
-        <v>370.79</v>
+        <v>350.88</v>
       </c>
       <c r="E48">
-        <v>379.29</v>
+        <v>371.86</v>
       </c>
       <c r="F48">
-        <v>151.9</v>
+        <v>160.06</v>
       </c>
       <c r="G48">
-        <v>103.25</v>
+        <v>106.05</v>
       </c>
       <c r="H48">
-        <v>63.25</v>
+        <v>66.05</v>
       </c>
       <c r="I48">
-        <v>208.5</v>
+        <v>210.9</v>
       </c>
       <c r="J48">
-        <v>118.5</v>
+        <v>120.9</v>
       </c>
       <c r="K48">
-        <v>11294</v>
+        <v>13511</v>
       </c>
       <c r="L48">
-        <v>3326.22</v>
+        <v>4281.78</v>
       </c>
       <c r="M48">
-        <v>6.39</v>
+        <v>166.51</v>
       </c>
       <c r="N48">
-        <v>158</v>
+        <v>243.95</v>
       </c>
       <c r="O48">
-        <v>6.91</v>
+        <v>170.76</v>
       </c>
       <c r="P48">
-        <v>72.08</v>
+        <v>74.08</v>
       </c>
       <c r="Q48">
-        <v>0.9</v>
+        <v>238.87</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>258.8</v>
       </c>
       <c r="S48">
-        <v>19349.88</v>
+        <v>22997.66</v>
       </c>
       <c r="T48">
-        <v>1429.28</v>
+        <v>41819.91</v>
       </c>
       <c r="U48">
-        <v>1191.06</v>
+        <v>34849.74</v>
       </c>
       <c r="V48">
-        <v>12</v>
+        <v>360</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -3816,64 +3816,64 @@
         <v>37</v>
       </c>
       <c r="C49">
-        <v>3089.9</v>
+        <v>2924.01</v>
       </c>
       <c r="D49">
-        <v>370.79</v>
+        <v>350.88</v>
       </c>
       <c r="E49">
-        <v>432.39</v>
+        <v>423.91</v>
       </c>
       <c r="F49">
-        <v>151.9</v>
+        <v>160.06</v>
       </c>
       <c r="G49">
-        <v>103.25</v>
+        <v>106.05</v>
       </c>
       <c r="H49">
-        <v>63.25</v>
+        <v>66.05</v>
       </c>
       <c r="I49">
-        <v>208.5</v>
+        <v>210.9</v>
       </c>
       <c r="J49">
-        <v>118.5</v>
+        <v>120.9</v>
       </c>
       <c r="K49">
-        <v>11294</v>
+        <v>13511</v>
       </c>
       <c r="L49">
-        <v>3326.22</v>
+        <v>4281.78</v>
       </c>
       <c r="M49">
-        <v>9.31</v>
+        <v>178.84</v>
       </c>
       <c r="N49">
-        <v>158</v>
+        <v>262.01</v>
       </c>
       <c r="O49">
-        <v>10.07</v>
+        <v>183.41</v>
       </c>
       <c r="P49">
-        <v>72.08</v>
+        <v>74.08</v>
       </c>
       <c r="Q49">
-        <v>1.11</v>
+        <v>261.03</v>
       </c>
       <c r="R49">
-        <v>36.7</v>
+        <v>258.1</v>
       </c>
       <c r="S49">
-        <v>19409.27</v>
+        <v>23114.91</v>
       </c>
       <c r="T49">
-        <v>2084.17</v>
+        <v>44917.03</v>
       </c>
       <c r="U49">
-        <v>1736.82</v>
+        <v>37430.61</v>
       </c>
       <c r="V49">
-        <v>17</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
@@ -3884,64 +3884,64 @@
         <v>38</v>
       </c>
       <c r="C50">
-        <v>3787.83</v>
+        <v>2214.55</v>
       </c>
       <c r="D50">
-        <v>454.54</v>
+        <v>265.75</v>
       </c>
       <c r="E50">
-        <v>839.73</v>
+        <v>518.55</v>
       </c>
       <c r="F50">
-        <v>331.42</v>
+        <v>185.05</v>
       </c>
       <c r="G50">
-        <v>158.21</v>
+        <v>119.8</v>
       </c>
       <c r="H50">
-        <v>124.85</v>
+        <v>83.55</v>
       </c>
       <c r="I50">
-        <v>325.3</v>
+        <v>241.9</v>
       </c>
       <c r="J50">
-        <v>171.3</v>
+        <v>0</v>
       </c>
       <c r="K50">
-        <v>21077</v>
+        <v>11395</v>
       </c>
       <c r="L50">
-        <v>6751.2</v>
+        <v>3213.6</v>
       </c>
       <c r="M50">
-        <v>10.84</v>
+        <v>75.27</v>
       </c>
       <c r="N50">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="O50">
-        <v>7.13</v>
+        <v>45.49</v>
       </c>
       <c r="P50">
-        <v>92.75</v>
+        <v>63.25</v>
       </c>
       <c r="Q50">
-        <v>1.18</v>
+        <v>99.93</v>
       </c>
       <c r="R50">
-        <v>37.7</v>
+        <v>222.8</v>
       </c>
       <c r="S50">
-        <v>34243.28</v>
+        <v>18626.69</v>
       </c>
       <c r="T50">
-        <v>2377.75</v>
+        <v>20994.86</v>
       </c>
       <c r="U50">
-        <v>1981.49</v>
+        <v>17495.79</v>
       </c>
       <c r="V50">
-        <v>25</v>
+        <v>213</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
@@ -3952,64 +3952,64 @@
         <v>38</v>
       </c>
       <c r="C51">
-        <v>3787.83</v>
+        <v>2214.55</v>
       </c>
       <c r="D51">
-        <v>454.54</v>
+        <v>265.75</v>
       </c>
       <c r="E51">
-        <v>839.73</v>
+        <v>518.55</v>
       </c>
       <c r="F51">
-        <v>331.42</v>
+        <v>185.05</v>
       </c>
       <c r="G51">
-        <v>158.21</v>
+        <v>119.8</v>
       </c>
       <c r="H51">
-        <v>124.85</v>
+        <v>83.55</v>
       </c>
       <c r="I51">
-        <v>325.3</v>
+        <v>241.9</v>
       </c>
       <c r="J51">
-        <v>171.3</v>
+        <v>0</v>
       </c>
       <c r="K51">
-        <v>21077</v>
+        <v>11395</v>
       </c>
       <c r="L51">
-        <v>6751.2</v>
+        <v>3213.6</v>
       </c>
       <c r="M51">
-        <v>10.58</v>
+        <v>78.52</v>
       </c>
       <c r="N51">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="O51">
-        <v>6.97</v>
+        <v>47.45</v>
       </c>
       <c r="P51">
-        <v>92.75</v>
+        <v>63.25</v>
       </c>
       <c r="Q51">
-        <v>0.98</v>
+        <v>114.32</v>
       </c>
       <c r="R51">
-        <v>47.8</v>
+        <v>191.2</v>
       </c>
       <c r="S51">
-        <v>34242.66</v>
+        <v>18646.29</v>
       </c>
       <c r="T51">
-        <v>2321.65</v>
+        <v>21899.3</v>
       </c>
       <c r="U51">
-        <v>1934.74</v>
+        <v>18249.53</v>
       </c>
       <c r="V51">
-        <v>26</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -4020,64 +4020,64 @@
         <v>38</v>
       </c>
       <c r="C52">
-        <v>3787.83</v>
+        <v>2214.55</v>
       </c>
       <c r="D52">
-        <v>454.54</v>
+        <v>265.75</v>
       </c>
       <c r="E52">
-        <v>736.6</v>
+        <v>454.86</v>
       </c>
       <c r="F52">
-        <v>331.42</v>
+        <v>185.05</v>
       </c>
       <c r="G52">
-        <v>158.21</v>
+        <v>119.8</v>
       </c>
       <c r="H52">
-        <v>124.85</v>
+        <v>83.55</v>
       </c>
       <c r="I52">
-        <v>325.3</v>
+        <v>241.9</v>
       </c>
       <c r="J52">
-        <v>171.3</v>
+        <v>0</v>
       </c>
       <c r="K52">
-        <v>21077</v>
+        <v>11395</v>
       </c>
       <c r="L52">
-        <v>6751.2</v>
+        <v>3213.6</v>
       </c>
       <c r="M52">
-        <v>17.25</v>
+        <v>88.51</v>
       </c>
       <c r="N52">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="O52">
-        <v>11.35</v>
+        <v>53.49</v>
       </c>
       <c r="P52">
-        <v>92.75</v>
+        <v>63.25</v>
       </c>
       <c r="Q52">
-        <v>1.62</v>
+        <v>129.61</v>
       </c>
       <c r="R52">
-        <v>79.2</v>
+        <v>208.4</v>
       </c>
       <c r="S52">
-        <v>34151.22</v>
+        <v>18613.92</v>
       </c>
       <c r="T52">
-        <v>3783.94</v>
+        <v>24687.86</v>
       </c>
       <c r="U52">
-        <v>3153.34</v>
+        <v>20573.29</v>
       </c>
       <c r="V52">
-        <v>41</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
@@ -4088,64 +4088,64 @@
         <v>38</v>
       </c>
       <c r="C53">
-        <v>3787.83</v>
+        <v>2214.55</v>
       </c>
       <c r="D53">
-        <v>454.54</v>
+        <v>265.75</v>
       </c>
       <c r="E53">
-        <v>736.6</v>
+        <v>454.86</v>
       </c>
       <c r="F53">
-        <v>331.42</v>
+        <v>185.05</v>
       </c>
       <c r="G53">
-        <v>158.21</v>
+        <v>119.8</v>
       </c>
       <c r="H53">
-        <v>124.85</v>
+        <v>83.55</v>
       </c>
       <c r="I53">
-        <v>325.3</v>
+        <v>241.9</v>
       </c>
       <c r="J53">
-        <v>171.3</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>21077</v>
+        <v>11395</v>
       </c>
       <c r="L53">
-        <v>6751.2</v>
+        <v>3213.6</v>
       </c>
       <c r="M53">
-        <v>13.81</v>
+        <v>102.25</v>
       </c>
       <c r="N53">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="O53">
-        <v>9.09</v>
+        <v>61.79</v>
       </c>
       <c r="P53">
-        <v>92.75</v>
+        <v>63.25</v>
       </c>
       <c r="Q53">
-        <v>1.49</v>
+        <v>145.24</v>
       </c>
       <c r="R53">
-        <v>70.4</v>
+        <v>257.7</v>
       </c>
       <c r="S53">
-        <v>34145.39</v>
+        <v>18651.59</v>
       </c>
       <c r="T53">
-        <v>3028.58</v>
+        <v>28519.81</v>
       </c>
       <c r="U53">
-        <v>2523.83</v>
+        <v>23766.74</v>
       </c>
       <c r="V53">
-        <v>32</v>
+        <v>282</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -4156,64 +4156,64 @@
         <v>38</v>
       </c>
       <c r="C54">
-        <v>3787.83</v>
+        <v>2214.55</v>
       </c>
       <c r="D54">
-        <v>454.54</v>
+        <v>265.75</v>
       </c>
       <c r="E54">
-        <v>736.6</v>
+        <v>454.86</v>
       </c>
       <c r="F54">
-        <v>331.42</v>
+        <v>185.05</v>
       </c>
       <c r="G54">
-        <v>158.21</v>
+        <v>119.8</v>
       </c>
       <c r="H54">
-        <v>124.85</v>
+        <v>83.55</v>
       </c>
       <c r="I54">
-        <v>325.3</v>
+        <v>241.9</v>
       </c>
       <c r="J54">
-        <v>171.3</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>21077</v>
+        <v>11395</v>
       </c>
       <c r="L54">
-        <v>6751.2</v>
+        <v>3213.6</v>
       </c>
       <c r="M54">
-        <v>12.36</v>
+        <v>95.9</v>
       </c>
       <c r="N54">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="O54">
-        <v>8.13</v>
+        <v>57.96</v>
       </c>
       <c r="P54">
-        <v>92.75</v>
+        <v>63.25</v>
       </c>
       <c r="Q54">
-        <v>1.42</v>
+        <v>128.83</v>
       </c>
       <c r="R54">
-        <v>12.9</v>
+        <v>228</v>
       </c>
       <c r="S54">
-        <v>34142.91</v>
+        <v>18625</v>
       </c>
       <c r="T54">
-        <v>2711.58</v>
+        <v>26749.25</v>
       </c>
       <c r="U54">
-        <v>2259.68</v>
+        <v>22291.14</v>
       </c>
       <c r="V54">
-        <v>28</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
@@ -4224,64 +4224,64 @@
         <v>38</v>
       </c>
       <c r="C55">
-        <v>3787.83</v>
+        <v>2214.55</v>
       </c>
       <c r="D55">
-        <v>454.54</v>
+        <v>265.75</v>
       </c>
       <c r="E55">
-        <v>795.53</v>
+        <v>491.25</v>
       </c>
       <c r="F55">
-        <v>331.42</v>
+        <v>185.05</v>
       </c>
       <c r="G55">
-        <v>158.21</v>
+        <v>119.8</v>
       </c>
       <c r="H55">
-        <v>124.85</v>
+        <v>83.55</v>
       </c>
       <c r="I55">
-        <v>325.3</v>
+        <v>241.9</v>
       </c>
       <c r="J55">
-        <v>171.3</v>
+        <v>0</v>
       </c>
       <c r="K55">
-        <v>21077</v>
+        <v>11395</v>
       </c>
       <c r="L55">
-        <v>6751.2</v>
+        <v>3213.6</v>
       </c>
       <c r="M55">
-        <v>15.35</v>
+        <v>87.33</v>
       </c>
       <c r="N55">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="O55">
-        <v>10.1</v>
+        <v>52.77</v>
       </c>
       <c r="P55">
-        <v>92.75</v>
+        <v>63.25</v>
       </c>
       <c r="Q55">
-        <v>1.48</v>
+        <v>126.29</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>124.4</v>
       </c>
       <c r="S55">
-        <v>34206.86</v>
+        <v>18645.09</v>
       </c>
       <c r="T55">
-        <v>3366.61</v>
+        <v>24356.51</v>
       </c>
       <c r="U55">
-        <v>2805.53</v>
+        <v>20297.28</v>
       </c>
       <c r="V55">
-        <v>34</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
@@ -4292,64 +4292,64 @@
         <v>38</v>
       </c>
       <c r="C56">
-        <v>3787.83</v>
+        <v>2214.55</v>
       </c>
       <c r="D56">
-        <v>454.54</v>
+        <v>265.75</v>
       </c>
       <c r="E56">
-        <v>795.53</v>
+        <v>491.25</v>
       </c>
       <c r="F56">
-        <v>331.42</v>
+        <v>185.05</v>
       </c>
       <c r="G56">
-        <v>158.21</v>
+        <v>119.8</v>
       </c>
       <c r="H56">
-        <v>124.85</v>
+        <v>83.55</v>
       </c>
       <c r="I56">
-        <v>325.3</v>
+        <v>241.9</v>
       </c>
       <c r="J56">
-        <v>171.3</v>
+        <v>0</v>
       </c>
       <c r="K56">
-        <v>21077</v>
+        <v>11395</v>
       </c>
       <c r="L56">
-        <v>6751.2</v>
+        <v>3213.6</v>
       </c>
       <c r="M56">
-        <v>9.6</v>
+        <v>93.85</v>
       </c>
       <c r="N56">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="O56">
-        <v>6.32</v>
+        <v>56.72</v>
       </c>
       <c r="P56">
-        <v>92.75</v>
+        <v>63.25</v>
       </c>
       <c r="Q56">
-        <v>1.13</v>
+        <v>131.96</v>
       </c>
       <c r="R56">
-        <v>37.2</v>
+        <v>104.3</v>
       </c>
       <c r="S56">
-        <v>34196.98</v>
+        <v>18661.23</v>
       </c>
       <c r="T56">
-        <v>2106.56</v>
+        <v>26176.34</v>
       </c>
       <c r="U56">
-        <v>1755.49</v>
+        <v>21813.81</v>
       </c>
       <c r="V56">
-        <v>22</v>
+        <v>267</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
@@ -4360,64 +4360,64 @@
         <v>38</v>
       </c>
       <c r="C57">
-        <v>3787.83</v>
+        <v>2214.55</v>
       </c>
       <c r="D57">
-        <v>454.54</v>
+        <v>265.75</v>
       </c>
       <c r="E57">
-        <v>795.53</v>
+        <v>491.25</v>
       </c>
       <c r="F57">
-        <v>331.42</v>
+        <v>185.05</v>
       </c>
       <c r="G57">
-        <v>158.21</v>
+        <v>119.8</v>
       </c>
       <c r="H57">
-        <v>124.85</v>
+        <v>83.55</v>
       </c>
       <c r="I57">
-        <v>325.3</v>
+        <v>241.9</v>
       </c>
       <c r="J57">
-        <v>171.3</v>
+        <v>0</v>
       </c>
       <c r="K57">
-        <v>21077</v>
+        <v>11395</v>
       </c>
       <c r="L57">
-        <v>6751.2</v>
+        <v>3213.6</v>
       </c>
       <c r="M57">
-        <v>9.86</v>
+        <v>94</v>
       </c>
       <c r="N57">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="O57">
-        <v>6.49</v>
+        <v>56.81</v>
       </c>
       <c r="P57">
-        <v>92.75</v>
+        <v>63.25</v>
       </c>
       <c r="Q57">
-        <v>0.82</v>
+        <v>135.54</v>
       </c>
       <c r="R57">
-        <v>17.8</v>
+        <v>247.6</v>
       </c>
       <c r="S57">
-        <v>34197.1</v>
+        <v>18665.05</v>
       </c>
       <c r="T57">
-        <v>2162.66</v>
+        <v>26219.14</v>
       </c>
       <c r="U57">
-        <v>1802.22</v>
+        <v>21849.47</v>
       </c>
       <c r="V57">
-        <v>25</v>
+        <v>255</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
@@ -4428,64 +4428,64 @@
         <v>38</v>
       </c>
       <c r="C58">
-        <v>3787.83</v>
+        <v>2214.55</v>
       </c>
       <c r="D58">
-        <v>454.54</v>
+        <v>265.75</v>
       </c>
       <c r="E58">
-        <v>736.6</v>
+        <v>454.86</v>
       </c>
       <c r="F58">
-        <v>331.42</v>
+        <v>185.05</v>
       </c>
       <c r="G58">
-        <v>158.21</v>
+        <v>119.8</v>
       </c>
       <c r="H58">
-        <v>124.85</v>
+        <v>83.55</v>
       </c>
       <c r="I58">
-        <v>325.3</v>
+        <v>241.9</v>
       </c>
       <c r="J58">
-        <v>171.3</v>
+        <v>0</v>
       </c>
       <c r="K58">
-        <v>21077</v>
+        <v>11395</v>
       </c>
       <c r="L58">
-        <v>6751.2</v>
+        <v>3213.6</v>
       </c>
       <c r="M58">
-        <v>11.99</v>
+        <v>100.34</v>
       </c>
       <c r="N58">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="O58">
-        <v>7.89</v>
+        <v>60.64</v>
       </c>
       <c r="P58">
-        <v>92.75</v>
+        <v>63.25</v>
       </c>
       <c r="Q58">
-        <v>1.28</v>
+        <v>143.94</v>
       </c>
       <c r="R58">
-        <v>40</v>
+        <v>160.7</v>
       </c>
       <c r="S58">
-        <v>34142.16</v>
+        <v>18647.23</v>
       </c>
       <c r="T58">
-        <v>2631.24</v>
+        <v>27985.35</v>
       </c>
       <c r="U58">
-        <v>2192.7</v>
+        <v>23321.31</v>
       </c>
       <c r="V58">
-        <v>28</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.25">
@@ -4496,64 +4496,64 @@
         <v>38</v>
       </c>
       <c r="C59">
-        <v>3787.83</v>
+        <v>2214.55</v>
       </c>
       <c r="D59">
-        <v>454.54</v>
+        <v>265.75</v>
       </c>
       <c r="E59">
-        <v>736.6</v>
+        <v>454.86</v>
       </c>
       <c r="F59">
-        <v>331.42</v>
+        <v>185.05</v>
       </c>
       <c r="G59">
-        <v>158.21</v>
+        <v>119.8</v>
       </c>
       <c r="H59">
-        <v>124.85</v>
+        <v>83.55</v>
       </c>
       <c r="I59">
-        <v>325.3</v>
+        <v>241.9</v>
       </c>
       <c r="J59">
-        <v>171.3</v>
+        <v>0</v>
       </c>
       <c r="K59">
-        <v>21077</v>
+        <v>11395</v>
       </c>
       <c r="L59">
-        <v>6751.2</v>
+        <v>3213.6</v>
       </c>
       <c r="M59">
-        <v>15.58</v>
+        <v>110.79</v>
       </c>
       <c r="N59">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="O59">
-        <v>10.25</v>
+        <v>66.95</v>
       </c>
       <c r="P59">
-        <v>92.75</v>
+        <v>63.25</v>
       </c>
       <c r="Q59">
-        <v>1.76</v>
+        <v>152.72</v>
       </c>
       <c r="R59">
-        <v>15.1</v>
+        <v>225.5</v>
       </c>
       <c r="S59">
-        <v>34148.59</v>
+        <v>18672.77</v>
       </c>
       <c r="T59">
-        <v>3418.29</v>
+        <v>30901.02</v>
       </c>
       <c r="U59">
-        <v>2848.61</v>
+        <v>25751.05</v>
       </c>
       <c r="V59">
-        <v>35</v>
+        <v>301</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
@@ -4564,64 +4564,64 @@
         <v>38</v>
       </c>
       <c r="C60">
-        <v>3787.83</v>
+        <v>2214.55</v>
       </c>
       <c r="D60">
-        <v>454.54</v>
+        <v>265.75</v>
       </c>
       <c r="E60">
-        <v>736.6</v>
+        <v>454.86</v>
       </c>
       <c r="F60">
-        <v>331.42</v>
+        <v>185.05</v>
       </c>
       <c r="G60">
-        <v>158.21</v>
+        <v>119.8</v>
       </c>
       <c r="H60">
-        <v>124.85</v>
+        <v>83.55</v>
       </c>
       <c r="I60">
-        <v>325.3</v>
+        <v>241.9</v>
       </c>
       <c r="J60">
-        <v>171.3</v>
+        <v>0</v>
       </c>
       <c r="K60">
-        <v>21077</v>
+        <v>11395</v>
       </c>
       <c r="L60">
-        <v>6751.2</v>
+        <v>3213.6</v>
       </c>
       <c r="M60">
-        <v>17.68</v>
+        <v>116.09</v>
       </c>
       <c r="N60">
-        <v>110</v>
+        <v>107.93</v>
       </c>
       <c r="O60">
-        <v>11.64</v>
+        <v>70.16</v>
       </c>
       <c r="P60">
-        <v>92.75</v>
+        <v>63.25</v>
       </c>
       <c r="Q60">
-        <v>1.99</v>
+        <v>166.2</v>
       </c>
       <c r="R60">
-        <v>30.3</v>
+        <v>210.8</v>
       </c>
       <c r="S60">
-        <v>34152.31</v>
+        <v>18697.69</v>
       </c>
       <c r="T60">
-        <v>3879.17</v>
+        <v>32379.92</v>
       </c>
       <c r="U60">
-        <v>3232.66</v>
+        <v>26983.32</v>
       </c>
       <c r="V60">
-        <v>39</v>
+        <v>310</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
@@ -4632,64 +4632,64 @@
         <v>38</v>
       </c>
       <c r="C61">
-        <v>3787.83</v>
+        <v>2214.55</v>
       </c>
       <c r="D61">
-        <v>454.54</v>
+        <v>265.75</v>
       </c>
       <c r="E61">
-        <v>839.73</v>
+        <v>518.55</v>
       </c>
       <c r="F61">
-        <v>331.42</v>
+        <v>185.05</v>
       </c>
       <c r="G61">
-        <v>158.21</v>
+        <v>119.8</v>
       </c>
       <c r="H61">
-        <v>124.85</v>
+        <v>83.55</v>
       </c>
       <c r="I61">
-        <v>325.3</v>
+        <v>241.9</v>
       </c>
       <c r="J61">
-        <v>171.3</v>
+        <v>0</v>
       </c>
       <c r="K61">
-        <v>21077</v>
+        <v>11395</v>
       </c>
       <c r="L61">
-        <v>6751.2</v>
+        <v>3213.6</v>
       </c>
       <c r="M61">
-        <v>16.53</v>
+        <v>144.23</v>
       </c>
       <c r="N61">
-        <v>110</v>
+        <v>134.09</v>
       </c>
       <c r="O61">
-        <v>10.88</v>
+        <v>87.16</v>
       </c>
       <c r="P61">
-        <v>92.75</v>
+        <v>63.25</v>
       </c>
       <c r="Q61">
-        <v>1.87</v>
+        <v>205.2</v>
       </c>
       <c r="R61">
-        <v>53.3</v>
+        <v>284.4</v>
       </c>
       <c r="S61">
-        <v>34253.41</v>
+        <v>18871.68</v>
       </c>
       <c r="T61">
-        <v>3627.19</v>
+        <v>40228.24</v>
       </c>
       <c r="U61">
-        <v>3022.66</v>
+        <v>33523.74</v>
       </c>
       <c r="V61">
-        <v>34</v>
+        <v>398</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
@@ -4700,64 +4700,64 @@
         <v>39</v>
       </c>
       <c r="C62">
-        <v>3293.91</v>
+        <v>2338.64</v>
       </c>
       <c r="D62">
-        <v>395.27</v>
+        <v>280.64</v>
       </c>
       <c r="E62">
-        <v>414.38</v>
+        <v>500.52</v>
       </c>
       <c r="F62">
-        <v>166.35</v>
+        <v>213.95</v>
       </c>
       <c r="G62">
-        <v>112.64</v>
+        <v>130.87</v>
       </c>
       <c r="H62">
-        <v>75.85</v>
+        <v>95.45</v>
       </c>
       <c r="I62">
-        <v>219.3</v>
+        <v>252.1</v>
       </c>
       <c r="J62">
-        <v>129.3</v>
+        <v>146.1</v>
       </c>
       <c r="K62">
-        <v>10479</v>
+        <v>10785.61</v>
       </c>
       <c r="L62">
-        <v>3324.43</v>
+        <v>3567.96</v>
       </c>
       <c r="M62">
-        <v>1.42</v>
+        <v>48.08</v>
       </c>
       <c r="N62">
-        <v>131</v>
+        <v>104.16</v>
       </c>
       <c r="O62">
-        <v>2.2</v>
+        <v>44.2</v>
       </c>
       <c r="P62">
-        <v>74.42</v>
+        <v>71.75</v>
       </c>
       <c r="Q62">
-        <v>0.21</v>
+        <v>71.27</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>133.6</v>
       </c>
       <c r="S62">
-        <v>18819.68</v>
+        <v>18651.3</v>
       </c>
       <c r="T62">
-        <v>471.23</v>
+        <v>15599.41</v>
       </c>
       <c r="U62">
-        <v>392.68</v>
+        <v>12999.38</v>
       </c>
       <c r="V62">
-        <v>6</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
@@ -4768,64 +4768,64 @@
         <v>39</v>
       </c>
       <c r="C63">
-        <v>3293.91</v>
+        <v>2338.64</v>
       </c>
       <c r="D63">
-        <v>395.27</v>
+        <v>280.64</v>
       </c>
       <c r="E63">
-        <v>414.38</v>
+        <v>500.52</v>
       </c>
       <c r="F63">
-        <v>166.35</v>
+        <v>213.95</v>
       </c>
       <c r="G63">
-        <v>112.64</v>
+        <v>130.87</v>
       </c>
       <c r="H63">
-        <v>75.85</v>
+        <v>95.45</v>
       </c>
       <c r="I63">
-        <v>219.3</v>
+        <v>252.1</v>
       </c>
       <c r="J63">
-        <v>129.3</v>
+        <v>146.1</v>
       </c>
       <c r="K63">
-        <v>10479</v>
+        <v>11446</v>
       </c>
       <c r="L63">
-        <v>3324.43</v>
+        <v>3779.28</v>
       </c>
       <c r="M63">
-        <v>2.76</v>
+        <v>51.01</v>
       </c>
       <c r="N63">
-        <v>131</v>
+        <v>104.16</v>
       </c>
       <c r="O63">
-        <v>4.26</v>
+        <v>46.9</v>
       </c>
       <c r="P63">
-        <v>74.42</v>
+        <v>71.75</v>
       </c>
       <c r="Q63">
-        <v>0.49</v>
+        <v>71.57</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>170.4</v>
       </c>
       <c r="S63">
-        <v>18823.36</v>
+        <v>19528.94</v>
       </c>
       <c r="T63">
-        <v>912.49</v>
+        <v>16551.82</v>
       </c>
       <c r="U63">
-        <v>760.42</v>
+        <v>13793.08</v>
       </c>
       <c r="V63">
-        <v>10</v>
+        <v>158</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
@@ -4836,64 +4836,64 @@
         <v>39</v>
       </c>
       <c r="C64">
-        <v>3293.91</v>
+        <v>2338.64</v>
       </c>
       <c r="D64">
-        <v>395.27</v>
+        <v>280.64</v>
       </c>
       <c r="E64">
-        <v>363.49</v>
+        <v>439.05</v>
       </c>
       <c r="F64">
-        <v>166.35</v>
+        <v>213.95</v>
       </c>
       <c r="G64">
-        <v>112.64</v>
+        <v>130.87</v>
       </c>
       <c r="H64">
-        <v>75.85</v>
+        <v>95.45</v>
       </c>
       <c r="I64">
-        <v>219.3</v>
+        <v>252.1</v>
       </c>
       <c r="J64">
-        <v>129.3</v>
+        <v>146.1</v>
       </c>
       <c r="K64">
-        <v>10479</v>
+        <v>11446</v>
       </c>
       <c r="L64">
-        <v>3324.43</v>
+        <v>3779.28</v>
       </c>
       <c r="M64">
-        <v>2.71</v>
+        <v>53.08</v>
       </c>
       <c r="N64">
-        <v>131</v>
+        <v>104.16</v>
       </c>
       <c r="O64">
-        <v>4.18</v>
+        <v>48.8</v>
       </c>
       <c r="P64">
-        <v>74.42</v>
+        <v>71.75</v>
       </c>
       <c r="Q64">
-        <v>0.36</v>
+        <v>76.65</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>115.8</v>
       </c>
       <c r="S64">
-        <v>18772.21</v>
+        <v>19476.52</v>
       </c>
       <c r="T64">
-        <v>896.11</v>
+        <v>17222.57</v>
       </c>
       <c r="U64">
-        <v>746.75</v>
+        <v>14352.11</v>
       </c>
       <c r="V64">
-        <v>9</v>
+        <v>165</v>
       </c>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.25">
@@ -4904,64 +4904,64 @@
         <v>39</v>
       </c>
       <c r="C65">
-        <v>3293.91</v>
+        <v>2338.64</v>
       </c>
       <c r="D65">
-        <v>395.27</v>
+        <v>280.64</v>
       </c>
       <c r="E65">
-        <v>363.49</v>
+        <v>439.05</v>
       </c>
       <c r="F65">
-        <v>166.35</v>
+        <v>213.95</v>
       </c>
       <c r="G65">
-        <v>112.64</v>
+        <v>130.87</v>
       </c>
       <c r="H65">
-        <v>75.85</v>
+        <v>95.45</v>
       </c>
       <c r="I65">
-        <v>219.3</v>
+        <v>252.1</v>
       </c>
       <c r="J65">
-        <v>129.3</v>
+        <v>146.1</v>
       </c>
       <c r="K65">
-        <v>10479</v>
+        <v>11446</v>
       </c>
       <c r="L65">
-        <v>3324.43</v>
+        <v>3779.28</v>
       </c>
       <c r="M65">
-        <v>3.62</v>
+        <v>57.16</v>
       </c>
       <c r="N65">
-        <v>131</v>
+        <v>104.16</v>
       </c>
       <c r="O65">
-        <v>5.59</v>
+        <v>52.55</v>
       </c>
       <c r="P65">
-        <v>74.42</v>
+        <v>71.75</v>
       </c>
       <c r="Q65">
-        <v>0.45</v>
+        <v>76.29</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>216.9</v>
       </c>
       <c r="S65">
-        <v>18774.62</v>
+        <v>19483.99</v>
       </c>
       <c r="T65">
-        <v>1198.57</v>
+        <v>18546.73</v>
       </c>
       <c r="U65">
-        <v>998.81</v>
+        <v>15455.55</v>
       </c>
       <c r="V65">
-        <v>11</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.25">
@@ -4972,64 +4972,64 @@
         <v>39</v>
       </c>
       <c r="C66">
-        <v>3293.91</v>
+        <v>2338.64</v>
       </c>
       <c r="D66">
-        <v>395.27</v>
+        <v>280.64</v>
       </c>
       <c r="E66">
-        <v>363.49</v>
+        <v>439.05</v>
       </c>
       <c r="F66">
-        <v>166.35</v>
+        <v>213.95</v>
       </c>
       <c r="G66">
-        <v>112.64</v>
+        <v>130.87</v>
       </c>
       <c r="H66">
-        <v>75.85</v>
+        <v>95.45</v>
       </c>
       <c r="I66">
-        <v>219.3</v>
+        <v>252.1</v>
       </c>
       <c r="J66">
-        <v>129.3</v>
+        <v>146.1</v>
       </c>
       <c r="K66">
-        <v>10479</v>
+        <v>10903.39</v>
       </c>
       <c r="L66">
-        <v>3324.43</v>
+        <v>3725.02</v>
       </c>
       <c r="M66">
-        <v>4.27</v>
+        <v>58.08</v>
       </c>
       <c r="N66">
-        <v>131</v>
+        <v>104.16</v>
       </c>
       <c r="O66">
-        <v>6.59</v>
+        <v>53.4</v>
       </c>
       <c r="P66">
-        <v>74.42</v>
+        <v>71.75</v>
       </c>
       <c r="Q66">
-        <v>0.61</v>
+        <v>74.78</v>
       </c>
       <c r="R66">
-        <v>11.8</v>
+        <v>150.6</v>
       </c>
       <c r="S66">
-        <v>18776.43</v>
+        <v>18887.38</v>
       </c>
       <c r="T66">
-        <v>1412.64</v>
+        <v>18845.47</v>
       </c>
       <c r="U66">
-        <v>1177.2</v>
+        <v>15704.51</v>
       </c>
       <c r="V66">
-        <v>16</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.25">
@@ -5040,64 +5040,64 @@
         <v>39</v>
       </c>
       <c r="C67">
-        <v>3293.91</v>
+        <v>2338.64</v>
       </c>
       <c r="D67">
-        <v>395.27</v>
+        <v>280.64</v>
       </c>
       <c r="E67">
-        <v>392.57</v>
+        <v>474.17</v>
       </c>
       <c r="F67">
-        <v>166.35</v>
+        <v>213.95</v>
       </c>
       <c r="G67">
-        <v>112.64</v>
+        <v>130.87</v>
       </c>
       <c r="H67">
-        <v>75.85</v>
+        <v>95.45</v>
       </c>
       <c r="I67">
-        <v>219.3</v>
+        <v>252.1</v>
       </c>
       <c r="J67">
-        <v>129.3</v>
+        <v>146.1</v>
       </c>
       <c r="K67">
-        <v>10479</v>
+        <v>11369.03</v>
       </c>
       <c r="L67">
-        <v>3324.43</v>
+        <v>3771.58</v>
       </c>
       <c r="M67">
-        <v>5.78</v>
+        <v>49.49</v>
       </c>
       <c r="N67">
-        <v>131</v>
+        <v>104.16</v>
       </c>
       <c r="O67">
-        <v>8.94</v>
+        <v>45.49</v>
       </c>
       <c r="P67">
-        <v>74.42</v>
+        <v>71.75</v>
       </c>
       <c r="Q67">
-        <v>0.74</v>
+        <v>70.91</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>145.8</v>
       </c>
       <c r="S67">
-        <v>18809.5</v>
+        <v>19414.33</v>
       </c>
       <c r="T67">
-        <v>1915.09</v>
+        <v>16055.84</v>
       </c>
       <c r="U67">
-        <v>1595.9</v>
+        <v>13379.79</v>
       </c>
       <c r="V67">
-        <v>19</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.25">
@@ -5108,64 +5108,64 @@
         <v>39</v>
       </c>
       <c r="C68">
-        <v>3293.91</v>
+        <v>2338.64</v>
       </c>
       <c r="D68">
-        <v>395.27</v>
+        <v>280.64</v>
       </c>
       <c r="E68">
-        <v>392.57</v>
+        <v>474.17</v>
       </c>
       <c r="F68">
-        <v>166.35</v>
+        <v>213.95</v>
       </c>
       <c r="G68">
-        <v>112.64</v>
+        <v>130.87</v>
       </c>
       <c r="H68">
-        <v>75.85</v>
+        <v>95.45</v>
       </c>
       <c r="I68">
-        <v>219.3</v>
+        <v>252.1</v>
       </c>
       <c r="J68">
-        <v>129.3</v>
+        <v>146.1</v>
       </c>
       <c r="K68">
-        <v>10479</v>
+        <v>10435.1</v>
       </c>
       <c r="L68">
-        <v>3324.43</v>
+        <v>3572.21</v>
       </c>
       <c r="M68">
-        <v>2.16</v>
+        <v>49.98</v>
       </c>
       <c r="N68">
-        <v>131</v>
+        <v>104.16</v>
       </c>
       <c r="O68">
-        <v>3.34</v>
+        <v>45.95</v>
       </c>
       <c r="P68">
-        <v>74.42</v>
+        <v>71.75</v>
       </c>
       <c r="Q68">
-        <v>0.29</v>
+        <v>77.5</v>
       </c>
       <c r="R68">
-        <v>11.9</v>
+        <v>199.3</v>
       </c>
       <c r="S68">
-        <v>18799.83</v>
+        <v>18288.57</v>
       </c>
       <c r="T68">
-        <v>716.13</v>
+        <v>16217.58</v>
       </c>
       <c r="U68">
-        <v>596.8</v>
+        <v>13514.53</v>
       </c>
       <c r="V68">
-        <v>9</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.25">
@@ -5176,64 +5176,64 @@
         <v>39</v>
       </c>
       <c r="C69">
-        <v>3293.91</v>
+        <v>2338.64</v>
       </c>
       <c r="D69">
-        <v>395.27</v>
+        <v>280.64</v>
       </c>
       <c r="E69">
-        <v>392.57</v>
+        <v>474.17</v>
       </c>
       <c r="F69">
-        <v>166.35</v>
+        <v>213.95</v>
       </c>
       <c r="G69">
-        <v>112.64</v>
+        <v>130.87</v>
       </c>
       <c r="H69">
-        <v>75.85</v>
+        <v>95.45</v>
       </c>
       <c r="I69">
-        <v>219.3</v>
+        <v>252.1</v>
       </c>
       <c r="J69">
-        <v>129.3</v>
+        <v>146.1</v>
       </c>
       <c r="K69">
-        <v>10479</v>
+        <v>10294.48</v>
       </c>
       <c r="L69">
-        <v>3324.43</v>
+        <v>3511.33</v>
       </c>
       <c r="M69">
-        <v>2.88</v>
+        <v>52.31</v>
       </c>
       <c r="N69">
-        <v>131</v>
+        <v>104.16</v>
       </c>
       <c r="O69">
-        <v>4.45</v>
+        <v>48.09</v>
       </c>
       <c r="P69">
-        <v>74.42</v>
+        <v>71.75</v>
       </c>
       <c r="Q69">
-        <v>0.44</v>
+        <v>89.18</v>
       </c>
       <c r="R69">
-        <v>13.6</v>
+        <v>237.2</v>
       </c>
       <c r="S69">
-        <v>18801.81</v>
+        <v>18103.22</v>
       </c>
       <c r="T69">
-        <v>953.18</v>
+        <v>16971.74</v>
       </c>
       <c r="U69">
-        <v>794.29</v>
+        <v>14143.06</v>
       </c>
       <c r="V69">
-        <v>14</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.25">
@@ -5244,64 +5244,64 @@
         <v>39</v>
       </c>
       <c r="C70">
-        <v>3293.91</v>
+        <v>2338.64</v>
       </c>
       <c r="D70">
-        <v>395.27</v>
+        <v>280.64</v>
       </c>
       <c r="E70">
-        <v>363.49</v>
+        <v>439.05</v>
       </c>
       <c r="F70">
-        <v>166.35</v>
+        <v>213.95</v>
       </c>
       <c r="G70">
-        <v>112.64</v>
+        <v>130.87</v>
       </c>
       <c r="H70">
-        <v>75.85</v>
+        <v>95.45</v>
       </c>
       <c r="I70">
-        <v>219.3</v>
+        <v>252.1</v>
       </c>
       <c r="J70">
-        <v>129.3</v>
+        <v>146.1</v>
       </c>
       <c r="K70">
-        <v>10479</v>
+        <v>9957.33</v>
       </c>
       <c r="L70">
-        <v>3324.43</v>
+        <v>3397.69</v>
       </c>
       <c r="M70">
-        <v>4.34</v>
+        <v>59.06</v>
       </c>
       <c r="N70">
-        <v>131</v>
+        <v>104.16</v>
       </c>
       <c r="O70">
-        <v>6.71</v>
+        <v>54.29</v>
       </c>
       <c r="P70">
-        <v>74.42</v>
+        <v>71.75</v>
       </c>
       <c r="Q70">
-        <v>0.85</v>
+        <v>84.58</v>
       </c>
       <c r="R70">
-        <v>16.9</v>
+        <v>188.7</v>
       </c>
       <c r="S70">
-        <v>18776.86</v>
+        <v>17625.66</v>
       </c>
       <c r="T70">
-        <v>1437.75</v>
+        <v>19161.26</v>
       </c>
       <c r="U70">
-        <v>1198.12</v>
+        <v>15967.69</v>
       </c>
       <c r="V70">
-        <v>13</v>
+        <v>180</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.25">
@@ -5312,64 +5312,64 @@
         <v>39</v>
       </c>
       <c r="C71">
-        <v>3293.91</v>
+        <v>2338.64</v>
       </c>
       <c r="D71">
-        <v>395.27</v>
+        <v>280.64</v>
       </c>
       <c r="E71">
-        <v>363.49</v>
+        <v>439.05</v>
       </c>
       <c r="F71">
-        <v>166.35</v>
+        <v>213.95</v>
       </c>
       <c r="G71">
-        <v>112.64</v>
+        <v>130.87</v>
       </c>
       <c r="H71">
-        <v>75.85</v>
+        <v>95.45</v>
       </c>
       <c r="I71">
-        <v>219.3</v>
+        <v>252.1</v>
       </c>
       <c r="J71">
-        <v>129.3</v>
+        <v>146.1</v>
       </c>
       <c r="K71">
-        <v>10479</v>
+        <v>11252.19</v>
       </c>
       <c r="L71">
-        <v>3324.43</v>
+        <v>3821.35</v>
       </c>
       <c r="M71">
-        <v>3.36</v>
+        <v>73.04</v>
       </c>
       <c r="N71">
-        <v>131</v>
+        <v>104.16</v>
       </c>
       <c r="O71">
-        <v>5.19</v>
+        <v>67.14</v>
       </c>
       <c r="P71">
-        <v>74.42</v>
+        <v>71.75</v>
       </c>
       <c r="Q71">
-        <v>0.54</v>
+        <v>104.91</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>185.8</v>
       </c>
       <c r="S71">
-        <v>18774.05</v>
+        <v>19391.34</v>
       </c>
       <c r="T71">
-        <v>1112.66</v>
+        <v>23698.16</v>
       </c>
       <c r="U71">
-        <v>927.21</v>
+        <v>19748.4</v>
       </c>
       <c r="V71">
-        <v>14</v>
+        <v>220</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.25">
@@ -5380,64 +5380,64 @@
         <v>39</v>
       </c>
       <c r="C72">
-        <v>3293.91</v>
+        <v>2338.64</v>
       </c>
       <c r="D72">
-        <v>395.27</v>
+        <v>280.64</v>
       </c>
       <c r="E72">
-        <v>363.49</v>
+        <v>439.05</v>
       </c>
       <c r="F72">
-        <v>166.35</v>
+        <v>213.95</v>
       </c>
       <c r="G72">
-        <v>112.64</v>
+        <v>130.87</v>
       </c>
       <c r="H72">
-        <v>75.85</v>
+        <v>95.45</v>
       </c>
       <c r="I72">
-        <v>219.3</v>
+        <v>252.1</v>
       </c>
       <c r="J72">
-        <v>129.3</v>
+        <v>146.1</v>
       </c>
       <c r="K72">
-        <v>10479</v>
+        <v>12627</v>
       </c>
       <c r="L72">
-        <v>3324.43</v>
+        <v>4261.29</v>
       </c>
       <c r="M72">
-        <v>3.24</v>
+        <v>66.36</v>
       </c>
       <c r="N72">
-        <v>131</v>
+        <v>104.16</v>
       </c>
       <c r="O72">
-        <v>5.01</v>
+        <v>61</v>
       </c>
       <c r="P72">
-        <v>74.42</v>
+        <v>71.75</v>
       </c>
       <c r="Q72">
-        <v>0.44</v>
+        <v>99.22</v>
       </c>
       <c r="R72">
-        <v>26.8</v>
+        <v>128.1</v>
       </c>
       <c r="S72">
-        <v>18773.65</v>
+        <v>21187.58</v>
       </c>
       <c r="T72">
-        <v>1073.44</v>
+        <v>21530.56</v>
       </c>
       <c r="U72">
-        <v>894.53</v>
+        <v>17942.01</v>
       </c>
       <c r="V72">
-        <v>11</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.25">
@@ -5448,64 +5448,64 @@
         <v>39</v>
       </c>
       <c r="C73">
-        <v>3293.91</v>
+        <v>2338.64</v>
       </c>
       <c r="D73">
-        <v>395.27</v>
+        <v>280.64</v>
       </c>
       <c r="E73">
-        <v>414.38</v>
+        <v>500.52</v>
       </c>
       <c r="F73">
-        <v>166.35</v>
+        <v>213.95</v>
       </c>
       <c r="G73">
-        <v>112.64</v>
+        <v>130.87</v>
       </c>
       <c r="H73">
-        <v>75.85</v>
+        <v>95.45</v>
       </c>
       <c r="I73">
-        <v>219.3</v>
+        <v>252.1</v>
       </c>
       <c r="J73">
-        <v>129.3</v>
+        <v>146.1</v>
       </c>
       <c r="K73">
-        <v>10479</v>
+        <v>12627</v>
       </c>
       <c r="L73">
-        <v>3324.43</v>
+        <v>4261.29</v>
       </c>
       <c r="M73">
-        <v>3.57</v>
+        <v>84.58</v>
       </c>
       <c r="N73">
-        <v>131</v>
+        <v>104.16</v>
       </c>
       <c r="O73">
-        <v>5.52</v>
+        <v>77.75</v>
       </c>
       <c r="P73">
-        <v>74.42</v>
+        <v>71.75</v>
       </c>
       <c r="Q73">
-        <v>0.6</v>
+        <v>130.32</v>
       </c>
       <c r="R73">
-        <v>35.7</v>
+        <v>114.8</v>
       </c>
       <c r="S73">
-        <v>18825.54</v>
+        <v>21315.12</v>
       </c>
       <c r="T73">
-        <v>1183.67</v>
+        <v>27441.52</v>
       </c>
       <c r="U73">
-        <v>986.37</v>
+        <v>22867.83</v>
       </c>
       <c r="V73">
-        <v>12</v>
+        <v>263</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.25">
@@ -5516,64 +5516,64 @@
         <v>40</v>
       </c>
       <c r="C74">
-        <v>3255.56</v>
+        <v>4159.84</v>
       </c>
       <c r="D74">
-        <v>390.67</v>
+        <v>499.18</v>
       </c>
       <c r="E74">
-        <v>330.42</v>
+        <v>422.72</v>
       </c>
       <c r="F74">
-        <v>135.75</v>
+        <v>181.65</v>
       </c>
       <c r="G74">
-        <v>103.25</v>
+        <v>118.5</v>
       </c>
       <c r="H74">
-        <v>63.25</v>
+        <v>82.15</v>
       </c>
       <c r="I74">
-        <v>208.5</v>
+        <v>240.7</v>
       </c>
       <c r="J74">
-        <v>118.5</v>
+        <v>134.7</v>
       </c>
       <c r="K74">
-        <v>9925</v>
+        <v>13442</v>
       </c>
       <c r="L74">
-        <v>2880.82</v>
+        <v>4316.25</v>
       </c>
       <c r="M74">
-        <v>3.45</v>
+        <v>92.17</v>
       </c>
       <c r="N74">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="O74">
-        <v>4.47</v>
+        <v>59.34</v>
       </c>
       <c r="P74">
-        <v>72.08</v>
+        <v>78.92</v>
       </c>
       <c r="Q74">
-        <v>0.68</v>
+        <v>89.27</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>172.3</v>
       </c>
       <c r="S74">
-        <v>17620.4</v>
+        <v>24020.39</v>
       </c>
       <c r="T74">
-        <v>993.92</v>
+        <v>17367.69</v>
       </c>
       <c r="U74">
-        <v>828.25</v>
+        <v>14473.21</v>
       </c>
       <c r="V74">
-        <v>7</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.25">
@@ -5584,64 +5584,64 @@
         <v>40</v>
       </c>
       <c r="C75">
-        <v>3255.56</v>
+        <v>4159.84</v>
       </c>
       <c r="D75">
-        <v>390.67</v>
+        <v>499.18</v>
       </c>
       <c r="E75">
-        <v>330.42</v>
+        <v>422.72</v>
       </c>
       <c r="F75">
-        <v>135.75</v>
+        <v>181.65</v>
       </c>
       <c r="G75">
-        <v>103.25</v>
+        <v>118.5</v>
       </c>
       <c r="H75">
-        <v>63.25</v>
+        <v>82.15</v>
       </c>
       <c r="I75">
-        <v>208.5</v>
+        <v>240.7</v>
       </c>
       <c r="J75">
-        <v>118.5</v>
+        <v>134.7</v>
       </c>
       <c r="K75">
-        <v>9925</v>
+        <v>13442</v>
       </c>
       <c r="L75">
-        <v>2880.82</v>
+        <v>4316.25</v>
       </c>
       <c r="M75">
-        <v>6.27</v>
+        <v>90.21</v>
       </c>
       <c r="N75">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="O75">
-        <v>8.12</v>
+        <v>58.08</v>
       </c>
       <c r="P75">
-        <v>72.08</v>
+        <v>78.92</v>
       </c>
       <c r="Q75">
-        <v>1.04</v>
+        <v>91.13</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>112.7</v>
       </c>
       <c r="S75">
-        <v>17627.23</v>
+        <v>24019.03</v>
       </c>
       <c r="T75">
-        <v>1804.49</v>
+        <v>16997.96</v>
       </c>
       <c r="U75">
-        <v>1503.74</v>
+        <v>14165.05</v>
       </c>
       <c r="V75">
-        <v>15</v>
+        <v>154</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.25">
@@ -5652,64 +5652,64 @@
         <v>40</v>
       </c>
       <c r="C76">
-        <v>3255.56</v>
+        <v>4159.84</v>
       </c>
       <c r="D76">
-        <v>390.67</v>
+        <v>499.18</v>
       </c>
       <c r="E76">
-        <v>289.84</v>
+        <v>370.8</v>
       </c>
       <c r="F76">
-        <v>135.75</v>
+        <v>181.65</v>
       </c>
       <c r="G76">
-        <v>103.25</v>
+        <v>118.5</v>
       </c>
       <c r="H76">
-        <v>63.25</v>
+        <v>82.15</v>
       </c>
       <c r="I76">
-        <v>208.5</v>
+        <v>240.7</v>
       </c>
       <c r="J76">
-        <v>118.5</v>
+        <v>134.7</v>
       </c>
       <c r="K76">
-        <v>9925</v>
+        <v>13442</v>
       </c>
       <c r="L76">
-        <v>2880.82</v>
+        <v>4316.25</v>
       </c>
       <c r="M76">
-        <v>4.99</v>
+        <v>111.86</v>
       </c>
       <c r="N76">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="O76">
-        <v>6.46</v>
+        <v>72.01</v>
       </c>
       <c r="P76">
-        <v>72.08</v>
+        <v>78.92</v>
       </c>
       <c r="Q76">
-        <v>0.77</v>
+        <v>113.92</v>
       </c>
       <c r="R76">
-        <v>27.6</v>
+        <v>87.1</v>
       </c>
       <c r="S76">
-        <v>17583.44</v>
+        <v>24025.48</v>
       </c>
       <c r="T76">
-        <v>1435.39</v>
+        <v>21076.84</v>
       </c>
       <c r="U76">
-        <v>1196.15</v>
+        <v>17564.18</v>
       </c>
       <c r="V76">
-        <v>13</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.25">
@@ -5720,64 +5720,64 @@
         <v>40</v>
       </c>
       <c r="C77">
-        <v>3255.56</v>
+        <v>4159.84</v>
       </c>
       <c r="D77">
-        <v>390.67</v>
+        <v>499.18</v>
       </c>
       <c r="E77">
-        <v>289.84</v>
+        <v>370.8</v>
       </c>
       <c r="F77">
-        <v>135.75</v>
+        <v>181.65</v>
       </c>
       <c r="G77">
-        <v>103.25</v>
+        <v>118.5</v>
       </c>
       <c r="H77">
-        <v>63.25</v>
+        <v>82.15</v>
       </c>
       <c r="I77">
-        <v>208.5</v>
+        <v>240.7</v>
       </c>
       <c r="J77">
-        <v>118.5</v>
+        <v>134.7</v>
       </c>
       <c r="K77">
-        <v>9925</v>
+        <v>13442</v>
       </c>
       <c r="L77">
-        <v>2880.82</v>
+        <v>4316.25</v>
       </c>
       <c r="M77">
-        <v>3.83</v>
+        <v>115.49</v>
       </c>
       <c r="N77">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="O77">
-        <v>4.96</v>
+        <v>74.35</v>
       </c>
       <c r="P77">
-        <v>72.08</v>
+        <v>78.92</v>
       </c>
       <c r="Q77">
-        <v>0.76</v>
+        <v>133.86</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="S77">
-        <v>17580.77</v>
+        <v>24051.39</v>
       </c>
       <c r="T77">
-        <v>1102.12</v>
+        <v>21761.84</v>
       </c>
       <c r="U77">
-        <v>918.42</v>
+        <v>18135.09</v>
       </c>
       <c r="V77">
-        <v>9</v>
+        <v>200</v>
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.25">
@@ -5788,64 +5788,64 @@
         <v>40</v>
       </c>
       <c r="C78">
-        <v>3255.56</v>
+        <v>4159.84</v>
       </c>
       <c r="D78">
-        <v>390.67</v>
+        <v>499.18</v>
       </c>
       <c r="E78">
-        <v>289.84</v>
+        <v>370.8</v>
       </c>
       <c r="F78">
-        <v>135.75</v>
+        <v>181.65</v>
       </c>
       <c r="G78">
-        <v>103.25</v>
+        <v>118.5</v>
       </c>
       <c r="H78">
-        <v>63.25</v>
+        <v>82.15</v>
       </c>
       <c r="I78">
-        <v>208.5</v>
+        <v>240.7</v>
       </c>
       <c r="J78">
-        <v>118.5</v>
+        <v>134.7</v>
       </c>
       <c r="K78">
-        <v>9925</v>
+        <v>13442</v>
       </c>
       <c r="L78">
-        <v>2880.82</v>
+        <v>4316.25</v>
       </c>
       <c r="M78">
-        <v>4.16</v>
+        <v>117.26</v>
       </c>
       <c r="N78">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="O78">
-        <v>5.38</v>
+        <v>75.49</v>
       </c>
       <c r="P78">
-        <v>72.08</v>
+        <v>78.92</v>
       </c>
       <c r="Q78">
-        <v>0.82</v>
+        <v>130.73</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="S78">
-        <v>17581.58</v>
+        <v>24051.17</v>
       </c>
       <c r="T78">
-        <v>1196.12</v>
+        <v>22094.88</v>
       </c>
       <c r="U78">
-        <v>996.77</v>
+        <v>18412.55</v>
       </c>
       <c r="V78">
-        <v>10</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.25">
@@ -5856,64 +5856,64 @@
         <v>40</v>
       </c>
       <c r="C79">
-        <v>3255.56</v>
+        <v>4159.84</v>
       </c>
       <c r="D79">
-        <v>390.67</v>
+        <v>499.18</v>
       </c>
       <c r="E79">
-        <v>313.03</v>
+        <v>400.47</v>
       </c>
       <c r="F79">
-        <v>135.75</v>
+        <v>181.65</v>
       </c>
       <c r="G79">
-        <v>103.25</v>
+        <v>118.5</v>
       </c>
       <c r="H79">
-        <v>63.25</v>
+        <v>82.15</v>
       </c>
       <c r="I79">
-        <v>208.5</v>
+        <v>240.7</v>
       </c>
       <c r="J79">
-        <v>118.5</v>
+        <v>134.7</v>
       </c>
       <c r="K79">
-        <v>9925</v>
+        <v>13442</v>
       </c>
       <c r="L79">
-        <v>2880.82</v>
+        <v>4316.25</v>
       </c>
       <c r="M79">
-        <v>4.26</v>
+        <v>91.75</v>
       </c>
       <c r="N79">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="O79">
-        <v>5.52</v>
+        <v>59.07</v>
       </c>
       <c r="P79">
-        <v>72.08</v>
+        <v>78.92</v>
       </c>
       <c r="Q79">
-        <v>0.75</v>
+        <v>93</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>126.1</v>
       </c>
       <c r="S79">
-        <v>17604.94</v>
+        <v>24001.18</v>
       </c>
       <c r="T79">
-        <v>1226.11</v>
+        <v>17288.19</v>
       </c>
       <c r="U79">
-        <v>1021.75</v>
+        <v>14406.91</v>
       </c>
       <c r="V79">
-        <v>11</v>
+        <v>156</v>
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.25">
@@ -5924,64 +5924,64 @@
         <v>40</v>
       </c>
       <c r="C80">
-        <v>3255.56</v>
+        <v>4159.84</v>
       </c>
       <c r="D80">
-        <v>390.67</v>
+        <v>499.18</v>
       </c>
       <c r="E80">
-        <v>313.03</v>
+        <v>400.47</v>
       </c>
       <c r="F80">
-        <v>135.75</v>
+        <v>181.65</v>
       </c>
       <c r="G80">
-        <v>103.25</v>
+        <v>118.5</v>
       </c>
       <c r="H80">
-        <v>63.25</v>
+        <v>82.15</v>
       </c>
       <c r="I80">
-        <v>208.5</v>
+        <v>240.7</v>
       </c>
       <c r="J80">
-        <v>118.5</v>
+        <v>134.7</v>
       </c>
       <c r="K80">
-        <v>9925</v>
+        <v>13442</v>
       </c>
       <c r="L80">
-        <v>2880.82</v>
+        <v>4316.25</v>
       </c>
       <c r="M80">
-        <v>2.95</v>
+        <v>105.01</v>
       </c>
       <c r="N80">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="O80">
-        <v>3.82</v>
+        <v>67.61</v>
       </c>
       <c r="P80">
-        <v>72.08</v>
+        <v>78.92</v>
       </c>
       <c r="Q80">
-        <v>0.46</v>
+        <v>103.38</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="S80">
-        <v>17601.64</v>
+        <v>24033.36</v>
       </c>
       <c r="T80">
-        <v>849.71</v>
+        <v>19786.78</v>
       </c>
       <c r="U80">
-        <v>708.09</v>
+        <v>16489.11</v>
       </c>
       <c r="V80">
-        <v>7</v>
+        <v>193</v>
       </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.25">
@@ -5992,64 +5992,64 @@
         <v>40</v>
       </c>
       <c r="C81">
-        <v>3255.56</v>
+        <v>4159.84</v>
       </c>
       <c r="D81">
-        <v>390.67</v>
+        <v>499.18</v>
       </c>
       <c r="E81">
-        <v>313.03</v>
+        <v>400.47</v>
       </c>
       <c r="F81">
-        <v>135.75</v>
+        <v>181.65</v>
       </c>
       <c r="G81">
-        <v>103.25</v>
+        <v>118.5</v>
       </c>
       <c r="H81">
-        <v>63.25</v>
+        <v>82.15</v>
       </c>
       <c r="I81">
-        <v>208.5</v>
+        <v>240.7</v>
       </c>
       <c r="J81">
-        <v>118.5</v>
+        <v>134.7</v>
       </c>
       <c r="K81">
-        <v>9925</v>
+        <v>13442</v>
       </c>
       <c r="L81">
-        <v>2880.82</v>
+        <v>4316.25</v>
       </c>
       <c r="M81">
-        <v>6.62</v>
+        <v>99.12</v>
       </c>
       <c r="N81">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="O81">
-        <v>8.57</v>
+        <v>63.81</v>
       </c>
       <c r="P81">
-        <v>72.08</v>
+        <v>78.92</v>
       </c>
       <c r="Q81">
-        <v>1.03</v>
+        <v>107.87</v>
       </c>
       <c r="R81">
-        <v>17.1</v>
+        <v>87.1</v>
       </c>
       <c r="S81">
-        <v>17610.63</v>
+        <v>24028.16</v>
       </c>
       <c r="T81">
-        <v>1903.91</v>
+        <v>18677.27</v>
       </c>
       <c r="U81">
-        <v>1586.6</v>
+        <v>15564.49</v>
       </c>
       <c r="V81">
-        <v>13</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.25">
@@ -6060,64 +6060,64 @@
         <v>40</v>
       </c>
       <c r="C82">
-        <v>3255.56</v>
+        <v>4159.84</v>
       </c>
       <c r="D82">
-        <v>390.67</v>
+        <v>499.18</v>
       </c>
       <c r="E82">
-        <v>289.84</v>
+        <v>370.8</v>
       </c>
       <c r="F82">
-        <v>135.75</v>
+        <v>181.65</v>
       </c>
       <c r="G82">
-        <v>103.25</v>
+        <v>118.5</v>
       </c>
       <c r="H82">
-        <v>63.25</v>
+        <v>82.15</v>
       </c>
       <c r="I82">
-        <v>208.5</v>
+        <v>240.7</v>
       </c>
       <c r="J82">
-        <v>118.5</v>
+        <v>134.7</v>
       </c>
       <c r="K82">
-        <v>9925</v>
+        <v>13442</v>
       </c>
       <c r="L82">
-        <v>2880.82</v>
+        <v>4316.25</v>
       </c>
       <c r="M82">
-        <v>3.45</v>
+        <v>112.43</v>
       </c>
       <c r="N82">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="O82">
-        <v>4.47</v>
+        <v>72.38</v>
       </c>
       <c r="P82">
-        <v>72.08</v>
+        <v>78.92</v>
       </c>
       <c r="Q82">
-        <v>0.44</v>
+        <v>110.48</v>
       </c>
       <c r="R82">
-        <v>47.3</v>
+        <v>184.2</v>
       </c>
       <c r="S82">
-        <v>17579.58</v>
+        <v>24022.98</v>
       </c>
       <c r="T82">
-        <v>993.31</v>
+        <v>21184.8</v>
       </c>
       <c r="U82">
-        <v>827.75</v>
+        <v>17654.11</v>
       </c>
       <c r="V82">
-        <v>7</v>
+        <v>191</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.25">
@@ -6128,64 +6128,64 @@
         <v>40</v>
       </c>
       <c r="C83">
-        <v>3255.56</v>
+        <v>4159.84</v>
       </c>
       <c r="D83">
-        <v>390.67</v>
+        <v>499.18</v>
       </c>
       <c r="E83">
-        <v>289.84</v>
+        <v>370.8</v>
       </c>
       <c r="F83">
-        <v>135.75</v>
+        <v>181.65</v>
       </c>
       <c r="G83">
-        <v>103.25</v>
+        <v>118.5</v>
       </c>
       <c r="H83">
-        <v>63.25</v>
+        <v>82.15</v>
       </c>
       <c r="I83">
-        <v>208.5</v>
+        <v>240.7</v>
       </c>
       <c r="J83">
-        <v>118.5</v>
+        <v>134.7</v>
       </c>
       <c r="K83">
-        <v>9925</v>
+        <v>13442</v>
       </c>
       <c r="L83">
-        <v>2880.82</v>
+        <v>4316.25</v>
       </c>
       <c r="M83">
-        <v>3.97</v>
+        <v>137.33</v>
       </c>
       <c r="N83">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="O83">
-        <v>5.14</v>
+        <v>88.41</v>
       </c>
       <c r="P83">
-        <v>72.08</v>
+        <v>78.92</v>
       </c>
       <c r="Q83">
-        <v>0.69</v>
+        <v>155.9</v>
       </c>
       <c r="R83">
-        <v>29.2</v>
+        <v>170.5</v>
       </c>
       <c r="S83">
-        <v>17581.02</v>
+        <v>24109.33</v>
       </c>
       <c r="T83">
-        <v>1142.64</v>
+        <v>25875.93</v>
       </c>
       <c r="U83">
-        <v>952.19</v>
+        <v>21563.41</v>
       </c>
       <c r="V83">
-        <v>7</v>
+        <v>236</v>
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.25">
@@ -6196,64 +6196,64 @@
         <v>40</v>
       </c>
       <c r="C84">
-        <v>3255.56</v>
+        <v>4159.84</v>
       </c>
       <c r="D84">
-        <v>390.67</v>
+        <v>499.18</v>
       </c>
       <c r="E84">
-        <v>289.84</v>
+        <v>370.8</v>
       </c>
       <c r="F84">
-        <v>135.75</v>
+        <v>181.65</v>
       </c>
       <c r="G84">
-        <v>103.25</v>
+        <v>118.5</v>
       </c>
       <c r="H84">
-        <v>63.25</v>
+        <v>82.15</v>
       </c>
       <c r="I84">
-        <v>208.5</v>
+        <v>240.7</v>
       </c>
       <c r="J84">
-        <v>118.5</v>
+        <v>134.7</v>
       </c>
       <c r="K84">
-        <v>9925</v>
+        <v>13442</v>
       </c>
       <c r="L84">
-        <v>2880.82</v>
+        <v>4316.25</v>
       </c>
       <c r="M84">
-        <v>7.42</v>
+        <v>128.01</v>
       </c>
       <c r="N84">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="O84">
-        <v>9.61</v>
+        <v>82.41</v>
       </c>
       <c r="P84">
-        <v>72.08</v>
+        <v>78.92</v>
       </c>
       <c r="Q84">
-        <v>1.25</v>
+        <v>138.05</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>217.3</v>
       </c>
       <c r="S84">
-        <v>17589.5</v>
+        <v>24076.16</v>
       </c>
       <c r="T84">
-        <v>2135.57</v>
+        <v>24120.17</v>
       </c>
       <c r="U84">
-        <v>1779.65</v>
+        <v>20100.3</v>
       </c>
       <c r="V84">
-        <v>14</v>
+        <v>232</v>
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.25">
@@ -6264,64 +6264,64 @@
         <v>40</v>
       </c>
       <c r="C85">
-        <v>3255.56</v>
+        <v>4159.84</v>
       </c>
       <c r="D85">
-        <v>390.67</v>
+        <v>499.18</v>
       </c>
       <c r="E85">
-        <v>330.42</v>
+        <v>422.72</v>
       </c>
       <c r="F85">
-        <v>135.75</v>
+        <v>181.65</v>
       </c>
       <c r="G85">
-        <v>103.25</v>
+        <v>118.5</v>
       </c>
       <c r="H85">
-        <v>63.25</v>
+        <v>82.15</v>
       </c>
       <c r="I85">
-        <v>208.5</v>
+        <v>240.7</v>
       </c>
       <c r="J85">
-        <v>118.5</v>
+        <v>134.7</v>
       </c>
       <c r="K85">
-        <v>9925</v>
+        <v>13442</v>
       </c>
       <c r="L85">
-        <v>2880.82</v>
+        <v>4316.25</v>
       </c>
       <c r="M85">
-        <v>6.87</v>
+        <v>166.72</v>
       </c>
       <c r="N85">
-        <v>128</v>
+        <v>104.72</v>
       </c>
       <c r="O85">
-        <v>8.89</v>
+        <v>107.33</v>
       </c>
       <c r="P85">
-        <v>72.08</v>
+        <v>78.92</v>
       </c>
       <c r="Q85">
-        <v>1.2</v>
+        <v>175.84</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>275.3</v>
       </c>
       <c r="S85">
-        <v>17628.76</v>
+        <v>24231.22</v>
       </c>
       <c r="T85">
-        <v>1976.22</v>
+        <v>31414.39</v>
       </c>
       <c r="U85">
-        <v>1646.84</v>
+        <v>26178.88</v>
       </c>
       <c r="V85">
-        <v>17</v>
+        <v>286</v>
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.25">
@@ -6332,64 +6332,64 @@
         <v>41</v>
       </c>
       <c r="C86">
-        <v>4655.77</v>
+        <v>4226.3</v>
       </c>
       <c r="D86">
-        <v>558.69</v>
+        <v>507.16</v>
       </c>
       <c r="E86">
-        <v>810.91</v>
+        <v>438.4</v>
       </c>
       <c r="F86">
-        <v>314.25</v>
+        <v>165.16</v>
       </c>
       <c r="G86">
-        <v>169.28</v>
+        <v>107.8</v>
       </c>
       <c r="H86">
-        <v>136.75</v>
+        <v>67.8</v>
       </c>
       <c r="I86">
-        <v>335.5</v>
+        <v>212.4</v>
       </c>
       <c r="J86">
-        <v>181.5</v>
+        <v>122.4</v>
       </c>
       <c r="K86">
-        <v>20276</v>
+        <v>12080</v>
       </c>
       <c r="L86">
-        <v>6743.5</v>
+        <v>3745.96</v>
       </c>
       <c r="M86">
-        <v>11.71</v>
+        <v>186.33</v>
       </c>
       <c r="N86">
-        <v>95</v>
+        <v>242.35</v>
       </c>
       <c r="O86">
-        <v>4.87</v>
+        <v>180.03</v>
       </c>
       <c r="P86">
-        <v>101.25</v>
+        <v>75.33</v>
       </c>
       <c r="Q86">
-        <v>1.51</v>
+        <v>213.49</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>286.6</v>
       </c>
       <c r="S86">
-        <v>34396.49</v>
+        <v>22570.91</v>
       </c>
       <c r="T86">
-        <v>2922.24</v>
+        <v>41546.01</v>
       </c>
       <c r="U86">
-        <v>2435.21</v>
+        <v>34621.69</v>
       </c>
       <c r="V86">
-        <v>32</v>
+        <v>322</v>
       </c>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.25">
@@ -6400,64 +6400,64 @@
         <v>41</v>
       </c>
       <c r="C87">
-        <v>4655.77</v>
+        <v>4226.3</v>
       </c>
       <c r="D87">
-        <v>558.69</v>
+        <v>507.16</v>
       </c>
       <c r="E87">
-        <v>810.91</v>
+        <v>438.4</v>
       </c>
       <c r="F87">
-        <v>314.25</v>
+        <v>165.16</v>
       </c>
       <c r="G87">
-        <v>169.28</v>
+        <v>107.8</v>
       </c>
       <c r="H87">
-        <v>136.75</v>
+        <v>67.8</v>
       </c>
       <c r="I87">
-        <v>335.5</v>
+        <v>212.4</v>
       </c>
       <c r="J87">
-        <v>181.5</v>
+        <v>122.4</v>
       </c>
       <c r="K87">
-        <v>20276</v>
+        <v>12080</v>
       </c>
       <c r="L87">
-        <v>6743.5</v>
+        <v>3745.96</v>
       </c>
       <c r="M87">
-        <v>11.29</v>
+        <v>194.75</v>
       </c>
       <c r="N87">
-        <v>95</v>
+        <v>253.3</v>
       </c>
       <c r="O87">
-        <v>4.7</v>
+        <v>188.16</v>
       </c>
       <c r="P87">
-        <v>101.25</v>
+        <v>75.33</v>
       </c>
       <c r="Q87">
-        <v>1.43</v>
+        <v>204.45</v>
       </c>
       <c r="R87">
-        <v>22.6</v>
+        <v>299.8</v>
       </c>
       <c r="S87">
-        <v>34395.82</v>
+        <v>22589.37</v>
       </c>
       <c r="T87">
-        <v>2817.91</v>
+        <v>43422.22</v>
       </c>
       <c r="U87">
-        <v>2348.28</v>
+        <v>36185.15</v>
       </c>
       <c r="V87">
-        <v>27</v>
+        <v>329</v>
       </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.25">
@@ -6468,64 +6468,64 @@
         <v>41</v>
       </c>
       <c r="C88">
-        <v>4655.77</v>
+        <v>4226.3</v>
       </c>
       <c r="D88">
-        <v>558.69</v>
+        <v>507.16</v>
       </c>
       <c r="E88">
-        <v>711.32</v>
+        <v>384.56</v>
       </c>
       <c r="F88">
-        <v>314.25</v>
+        <v>165.16</v>
       </c>
       <c r="G88">
-        <v>169.28</v>
+        <v>107.8</v>
       </c>
       <c r="H88">
-        <v>136.75</v>
+        <v>67.8</v>
       </c>
       <c r="I88">
-        <v>335.5</v>
+        <v>212.4</v>
       </c>
       <c r="J88">
-        <v>181.5</v>
+        <v>122.4</v>
       </c>
       <c r="K88">
-        <v>20276</v>
+        <v>12080</v>
       </c>
       <c r="L88">
-        <v>6743.5</v>
+        <v>3745.96</v>
       </c>
       <c r="M88">
-        <v>12.4</v>
+        <v>227.46</v>
       </c>
       <c r="N88">
-        <v>95</v>
+        <v>295.84</v>
       </c>
       <c r="O88">
-        <v>5.16</v>
+        <v>219.77</v>
       </c>
       <c r="P88">
-        <v>101.25</v>
+        <v>75.33</v>
       </c>
       <c r="Q88">
-        <v>1.56</v>
+        <v>269.03</v>
       </c>
       <c r="R88">
-        <v>20.2</v>
+        <v>406.4</v>
       </c>
       <c r="S88">
-        <v>34297.93</v>
+        <v>22706.97</v>
       </c>
       <c r="T88">
-        <v>3094.49</v>
+        <v>50715.76</v>
       </c>
       <c r="U88">
-        <v>2578.77</v>
+        <v>42263.08</v>
       </c>
       <c r="V88">
-        <v>31</v>
+        <v>428</v>
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.25">
@@ -6536,64 +6536,64 @@
         <v>41</v>
       </c>
       <c r="C89">
-        <v>4655.77</v>
+        <v>4226.3</v>
       </c>
       <c r="D89">
-        <v>558.69</v>
+        <v>507.16</v>
       </c>
       <c r="E89">
-        <v>711.32</v>
+        <v>384.56</v>
       </c>
       <c r="F89">
-        <v>314.25</v>
+        <v>165.16</v>
       </c>
       <c r="G89">
-        <v>169.28</v>
+        <v>107.8</v>
       </c>
       <c r="H89">
-        <v>136.75</v>
+        <v>67.8</v>
       </c>
       <c r="I89">
-        <v>335.5</v>
+        <v>212.4</v>
       </c>
       <c r="J89">
-        <v>181.5</v>
+        <v>122.4</v>
       </c>
       <c r="K89">
-        <v>20276</v>
+        <v>12080</v>
       </c>
       <c r="L89">
-        <v>6743.5</v>
+        <v>3745.96</v>
       </c>
       <c r="M89">
-        <v>13.38</v>
+        <v>229.94</v>
       </c>
       <c r="N89">
-        <v>95</v>
+        <v>299.07</v>
       </c>
       <c r="O89">
-        <v>5.56</v>
+        <v>222.17</v>
       </c>
       <c r="P89">
-        <v>101.25</v>
+        <v>75.33</v>
       </c>
       <c r="Q89">
-        <v>1.93</v>
+        <v>266.41</v>
       </c>
       <c r="R89">
-        <v>29.1</v>
+        <v>346.6</v>
       </c>
       <c r="S89">
-        <v>34299.68</v>
+        <v>22712.46</v>
       </c>
       <c r="T89">
-        <v>3338.84</v>
+        <v>51269.07</v>
       </c>
       <c r="U89">
-        <v>2782.37</v>
+        <v>42724.07</v>
       </c>
       <c r="V89">
-        <v>34</v>
+        <v>413</v>
       </c>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.25">
@@ -6604,64 +6604,64 @@
         <v>41</v>
       </c>
       <c r="C90">
-        <v>4655.77</v>
+        <v>4226.3</v>
       </c>
       <c r="D90">
-        <v>558.69</v>
+        <v>507.16</v>
       </c>
       <c r="E90">
-        <v>711.32</v>
+        <v>384.56</v>
       </c>
       <c r="F90">
-        <v>314.25</v>
+        <v>165.16</v>
       </c>
       <c r="G90">
-        <v>169.28</v>
+        <v>107.8</v>
       </c>
       <c r="H90">
-        <v>136.75</v>
+        <v>67.8</v>
       </c>
       <c r="I90">
-        <v>335.5</v>
+        <v>212.4</v>
       </c>
       <c r="J90">
-        <v>181.5</v>
+        <v>122.4</v>
       </c>
       <c r="K90">
-        <v>20276</v>
+        <v>12080</v>
       </c>
       <c r="L90">
-        <v>6743.5</v>
+        <v>3745.96</v>
       </c>
       <c r="M90">
-        <v>13.51</v>
+        <v>232.84</v>
       </c>
       <c r="N90">
-        <v>95</v>
+        <v>302.84</v>
       </c>
       <c r="O90">
-        <v>5.62</v>
+        <v>224.97</v>
       </c>
       <c r="P90">
-        <v>101.25</v>
+        <v>75.33</v>
       </c>
       <c r="Q90">
-        <v>1.58</v>
+        <v>285.87</v>
       </c>
       <c r="R90">
-        <v>26</v>
+        <v>253</v>
       </c>
       <c r="S90">
-        <v>34299.52</v>
+        <v>22741.39</v>
       </c>
       <c r="T90">
-        <v>3371.95</v>
+        <v>51915.88</v>
       </c>
       <c r="U90">
-        <v>2809.98</v>
+        <v>43263.07</v>
       </c>
       <c r="V90">
-        <v>35</v>
+        <v>418</v>
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.25">
@@ -6672,64 +6672,64 @@
         <v>41</v>
       </c>
       <c r="C91">
-        <v>4655.77</v>
+        <v>4226.3</v>
       </c>
       <c r="D91">
-        <v>558.69</v>
+        <v>507.16</v>
       </c>
       <c r="E91">
-        <v>768.23</v>
+        <v>415.32</v>
       </c>
       <c r="F91">
-        <v>314.25</v>
+        <v>165.16</v>
       </c>
       <c r="G91">
-        <v>169.28</v>
+        <v>107.8</v>
       </c>
       <c r="H91">
-        <v>136.75</v>
+        <v>67.8</v>
       </c>
       <c r="I91">
-        <v>335.5</v>
+        <v>212.4</v>
       </c>
       <c r="J91">
-        <v>181.5</v>
+        <v>122.4</v>
       </c>
       <c r="K91">
-        <v>20276</v>
+        <v>12080</v>
       </c>
       <c r="L91">
-        <v>6743.5</v>
+        <v>3745.96</v>
       </c>
       <c r="M91">
-        <v>13.29</v>
+        <v>210.41</v>
       </c>
       <c r="N91">
-        <v>95</v>
+        <v>273.67</v>
       </c>
       <c r="O91">
-        <v>5.53</v>
+        <v>203.3</v>
       </c>
       <c r="P91">
-        <v>101.25</v>
+        <v>75.33</v>
       </c>
       <c r="Q91">
-        <v>1.82</v>
+        <v>256.82</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>376.6</v>
       </c>
       <c r="S91">
-        <v>34356.36</v>
+        <v>22669.83</v>
       </c>
       <c r="T91">
-        <v>3315.64</v>
+        <v>46914.89</v>
       </c>
       <c r="U91">
-        <v>2763.08</v>
+        <v>39095.69</v>
       </c>
       <c r="V91">
-        <v>34</v>
+        <v>362</v>
       </c>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.25">
@@ -6740,64 +6740,64 @@
         <v>41</v>
       </c>
       <c r="C92">
-        <v>4655.77</v>
+        <v>4226.3</v>
       </c>
       <c r="D92">
-        <v>558.69</v>
+        <v>507.16</v>
       </c>
       <c r="E92">
-        <v>768.23</v>
+        <v>415.32</v>
       </c>
       <c r="F92">
-        <v>314.25</v>
+        <v>165.16</v>
       </c>
       <c r="G92">
-        <v>169.28</v>
+        <v>107.8</v>
       </c>
       <c r="H92">
-        <v>136.75</v>
+        <v>67.8</v>
       </c>
       <c r="I92">
-        <v>335.5</v>
+        <v>212.4</v>
       </c>
       <c r="J92">
-        <v>181.5</v>
+        <v>122.4</v>
       </c>
       <c r="K92">
-        <v>20276</v>
+        <v>12080</v>
       </c>
       <c r="L92">
-        <v>6743.5</v>
+        <v>3745.96</v>
       </c>
       <c r="M92">
-        <v>7.67</v>
+        <v>204.07</v>
       </c>
       <c r="N92">
-        <v>95</v>
+        <v>265.42</v>
       </c>
       <c r="O92">
-        <v>3.19</v>
+        <v>197.17</v>
       </c>
       <c r="P92">
-        <v>101.25</v>
+        <v>75.33</v>
       </c>
       <c r="Q92">
-        <v>1.1</v>
+        <v>247.3</v>
       </c>
       <c r="R92">
-        <v>43.6</v>
+        <v>232.6</v>
       </c>
       <c r="S92">
-        <v>34347.68</v>
+        <v>22639.59</v>
       </c>
       <c r="T92">
-        <v>1915.46</v>
+        <v>45500.87</v>
       </c>
       <c r="U92">
-        <v>1596.23</v>
+        <v>37917.33</v>
       </c>
       <c r="V92">
-        <v>19</v>
+        <v>344</v>
       </c>
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.25">
@@ -6808,64 +6808,64 @@
         <v>41</v>
       </c>
       <c r="C93">
-        <v>4655.77</v>
+        <v>4226.3</v>
       </c>
       <c r="D93">
-        <v>558.69</v>
+        <v>507.16</v>
       </c>
       <c r="E93">
-        <v>768.23</v>
+        <v>415.32</v>
       </c>
       <c r="F93">
-        <v>314.25</v>
+        <v>165.16</v>
       </c>
       <c r="G93">
-        <v>169.28</v>
+        <v>107.8</v>
       </c>
       <c r="H93">
-        <v>136.75</v>
+        <v>67.8</v>
       </c>
       <c r="I93">
-        <v>335.5</v>
+        <v>212.4</v>
       </c>
       <c r="J93">
-        <v>181.5</v>
+        <v>122.4</v>
       </c>
       <c r="K93">
-        <v>20276</v>
+        <v>12080</v>
       </c>
       <c r="L93">
-        <v>6743.5</v>
+        <v>3745.96</v>
       </c>
       <c r="M93">
-        <v>12.6</v>
+        <v>227.98</v>
       </c>
       <c r="N93">
-        <v>95</v>
+        <v>296.51</v>
       </c>
       <c r="O93">
-        <v>5.24</v>
+        <v>220.27</v>
       </c>
       <c r="P93">
-        <v>101.25</v>
+        <v>75.33</v>
       </c>
       <c r="Q93">
-        <v>1.49</v>
+        <v>271.72</v>
       </c>
       <c r="R93">
-        <v>25.3</v>
+        <v>364</v>
       </c>
       <c r="S93">
-        <v>34355.05</v>
+        <v>22742.11</v>
       </c>
       <c r="T93">
-        <v>3143.56</v>
+        <v>50830.76</v>
       </c>
       <c r="U93">
-        <v>2619.66</v>
+        <v>42358.83</v>
       </c>
       <c r="V93">
-        <v>33</v>
+        <v>393</v>
       </c>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.25">
@@ -6876,64 +6876,64 @@
         <v>41</v>
       </c>
       <c r="C94">
-        <v>4655.77</v>
+        <v>4226.3</v>
       </c>
       <c r="D94">
-        <v>558.69</v>
+        <v>507.16</v>
       </c>
       <c r="E94">
-        <v>711.32</v>
+        <v>384.56</v>
       </c>
       <c r="F94">
-        <v>314.25</v>
+        <v>165.16</v>
       </c>
       <c r="G94">
-        <v>169.28</v>
+        <v>107.8</v>
       </c>
       <c r="H94">
-        <v>136.75</v>
+        <v>67.8</v>
       </c>
       <c r="I94">
-        <v>335.5</v>
+        <v>212.4</v>
       </c>
       <c r="J94">
-        <v>181.5</v>
+        <v>122.4</v>
       </c>
       <c r="K94">
-        <v>20276</v>
+        <v>12080</v>
       </c>
       <c r="L94">
-        <v>6743.5</v>
+        <v>3745.96</v>
       </c>
       <c r="M94">
-        <v>15.73</v>
+        <v>228.97</v>
       </c>
       <c r="N94">
-        <v>95</v>
+        <v>297.81</v>
       </c>
       <c r="O94">
-        <v>6.54</v>
+        <v>221.23</v>
       </c>
       <c r="P94">
-        <v>101.25</v>
+        <v>75.33</v>
       </c>
       <c r="Q94">
-        <v>2.23</v>
+        <v>271.24</v>
       </c>
       <c r="R94">
-        <v>42.9</v>
+        <v>375.8</v>
       </c>
       <c r="S94">
-        <v>34303.31</v>
+        <v>22714.12</v>
       </c>
       <c r="T94">
-        <v>3925.85</v>
+        <v>51052.87</v>
       </c>
       <c r="U94">
-        <v>3271.59</v>
+        <v>42543.9</v>
       </c>
       <c r="V94">
-        <v>35</v>
+        <v>393</v>
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.25">
@@ -6944,64 +6944,64 @@
         <v>41</v>
       </c>
       <c r="C95">
-        <v>4655.77</v>
+        <v>4226.3</v>
       </c>
       <c r="D95">
-        <v>558.69</v>
+        <v>507.16</v>
       </c>
       <c r="E95">
-        <v>711.32</v>
+        <v>384.56</v>
       </c>
       <c r="F95">
-        <v>314.25</v>
+        <v>165.16</v>
       </c>
       <c r="G95">
-        <v>169.28</v>
+        <v>107.8</v>
       </c>
       <c r="H95">
-        <v>136.75</v>
+        <v>67.8</v>
       </c>
       <c r="I95">
-        <v>335.5</v>
+        <v>212.4</v>
       </c>
       <c r="J95">
-        <v>181.5</v>
+        <v>122.4</v>
       </c>
       <c r="K95">
-        <v>20276</v>
+        <v>12080</v>
       </c>
       <c r="L95">
-        <v>6743.5</v>
+        <v>3745.96</v>
       </c>
       <c r="M95">
-        <v>12.49</v>
+        <v>260.43</v>
       </c>
       <c r="N95">
-        <v>95</v>
+        <v>338.73</v>
       </c>
       <c r="O95">
-        <v>5.2</v>
+        <v>251.63</v>
       </c>
       <c r="P95">
-        <v>101.25</v>
+        <v>75.33</v>
       </c>
       <c r="Q95">
-        <v>1.66</v>
+        <v>295.94</v>
       </c>
       <c r="R95">
-        <v>43.8</v>
+        <v>529.1</v>
       </c>
       <c r="S95">
-        <v>34298.16</v>
+        <v>22841.6</v>
       </c>
       <c r="T95">
-        <v>3117.62</v>
+        <v>58067.89</v>
       </c>
       <c r="U95">
-        <v>2598.05</v>
+        <v>48389.7</v>
       </c>
       <c r="V95">
-        <v>29</v>
+        <v>476</v>
       </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.25">
@@ -7012,64 +7012,64 @@
         <v>41</v>
       </c>
       <c r="C96">
-        <v>4655.77</v>
+        <v>4226.3</v>
       </c>
       <c r="D96">
-        <v>558.69</v>
+        <v>507.16</v>
       </c>
       <c r="E96">
-        <v>711.32</v>
+        <v>384.56</v>
       </c>
       <c r="F96">
-        <v>314.25</v>
+        <v>165.16</v>
       </c>
       <c r="G96">
-        <v>169.28</v>
+        <v>107.8</v>
       </c>
       <c r="H96">
-        <v>136.75</v>
+        <v>67.8</v>
       </c>
       <c r="I96">
-        <v>335.5</v>
+        <v>212.4</v>
       </c>
       <c r="J96">
-        <v>181.5</v>
+        <v>122.4</v>
       </c>
       <c r="K96">
-        <v>20276</v>
+        <v>12080</v>
       </c>
       <c r="L96">
-        <v>6743.5</v>
+        <v>3745.96</v>
       </c>
       <c r="M96">
-        <v>15.6</v>
+        <v>274.84</v>
       </c>
       <c r="N96">
-        <v>95</v>
+        <v>357.47</v>
       </c>
       <c r="O96">
-        <v>6.49</v>
+        <v>265.55</v>
       </c>
       <c r="P96">
-        <v>101.25</v>
+        <v>75.33</v>
       </c>
       <c r="Q96">
-        <v>2.38</v>
+        <v>334.72</v>
       </c>
       <c r="R96">
-        <v>34</v>
+        <v>582.6</v>
       </c>
       <c r="S96">
-        <v>34303.28</v>
+        <v>22927.45</v>
       </c>
       <c r="T96">
-        <v>3894.04</v>
+        <v>61280.73</v>
       </c>
       <c r="U96">
-        <v>3245.04</v>
+        <v>51067.16</v>
       </c>
       <c r="V96">
-        <v>39</v>
+        <v>476</v>
       </c>
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.25">
@@ -7080,64 +7080,64 @@
         <v>41</v>
       </c>
       <c r="C97">
-        <v>4655.77</v>
+        <v>4226.3</v>
       </c>
       <c r="D97">
-        <v>558.69</v>
+        <v>507.16</v>
       </c>
       <c r="E97">
-        <v>810.91</v>
+        <v>438.4</v>
       </c>
       <c r="F97">
-        <v>314.25</v>
+        <v>165.16</v>
       </c>
       <c r="G97">
-        <v>169.28</v>
+        <v>107.8</v>
       </c>
       <c r="H97">
-        <v>136.75</v>
+        <v>67.8</v>
       </c>
       <c r="I97">
-        <v>335.5</v>
+        <v>212.4</v>
       </c>
       <c r="J97">
-        <v>181.5</v>
+        <v>122.4</v>
       </c>
       <c r="K97">
-        <v>20276</v>
+        <v>12080</v>
       </c>
       <c r="L97">
-        <v>6743.5</v>
+        <v>3745.96</v>
       </c>
       <c r="M97">
-        <v>17.91</v>
+        <v>289.99</v>
       </c>
       <c r="N97">
-        <v>95</v>
+        <v>377.17</v>
       </c>
       <c r="O97">
-        <v>7.45</v>
+        <v>280.19</v>
       </c>
       <c r="P97">
-        <v>101.25</v>
+        <v>75.33</v>
       </c>
       <c r="Q97">
-        <v>2.76</v>
+        <v>349.9</v>
       </c>
       <c r="R97">
-        <v>51.8</v>
+        <v>483.7</v>
       </c>
       <c r="S97">
-        <v>34406.52</v>
+        <v>23045.96</v>
       </c>
       <c r="T97">
-        <v>4469.76</v>
+        <v>64658.68</v>
       </c>
       <c r="U97">
-        <v>3724.84</v>
+        <v>53882.02</v>
       </c>
       <c r="V97">
-        <v>43</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
